--- a/template.xlsx
+++ b/template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\recipe-app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A54FE393-DA8F-48E9-B82F-CABCF7CD0418}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77D3A35-40BC-47F8-82DD-081E887FE95D}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,7 +108,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,14 +147,6 @@
     </font>
     <font>
       <sz val="18"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="major"/>
@@ -206,6 +198,22 @@
     </font>
     <font>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -712,9 +720,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -734,9 +739,6 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -749,8 +751,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
@@ -782,9 +784,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="3" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -794,9 +796,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -813,67 +815,75 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1402,106 +1412,106 @@
   <sheetData>
     <row r="1" spans="1:26" ht="24.6" customHeight="1">
       <c r="A1" s="12"/>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
       <c r="H1" s="13"/>
       <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
       <c r="H2" s="14"/>
     </row>
     <row r="3" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
+      <c r="A3" s="88"/>
+      <c r="B3" s="101"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
       <c r="H3" s="14"/>
     </row>
     <row r="4" spans="1:26" ht="24.6" customHeight="1">
       <c r="A4" s="15"/>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
       <c r="H4" s="14"/>
     </row>
     <row r="5" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="50"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="48"/>
       <c r="H5" s="14"/>
     </row>
     <row r="6" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A6" s="79"/>
-      <c r="B6" s="80"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="50"/>
+      <c r="A6" s="88"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="48"/>
       <c r="H6" s="16"/>
     </row>
     <row r="7" spans="1:26" ht="35.450000000000003" customHeight="1">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="86" t="s">
+      <c r="B7" s="59"/>
+      <c r="C7" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="86"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="62" t="s">
+      <c r="D7" s="99"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="62"/>
+      <c r="G7" s="60"/>
       <c r="H7" s="16"/>
     </row>
     <row r="8" spans="1:26" ht="33.6" customHeight="1">
-      <c r="A8" s="38"/>
-      <c r="B8" s="61"/>
-      <c r="C8" s="87"/>
-      <c r="D8" s="87"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="83" t="e">
+      <c r="A8" s="36"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="100"/>
+      <c r="D8" s="100"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="98" t="e">
         <f>A8/C8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G8" s="83"/>
+      <c r="G8" s="98"/>
       <c r="H8" s="14"/>
     </row>
     <row r="9" spans="1:26" ht="24.6" customHeight="1">
       <c r="A9" s="15"/>
-      <c r="B9" s="63"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
       <c r="H9" s="17"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -1509,37 +1519,37 @@
     </row>
     <row r="10" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
       <c r="A10" s="15"/>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
       <c r="H10" s="14"/>
     </row>
     <row r="11" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A11" s="84" t="s">
+      <c r="A11" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="84" t="s">
+      <c r="C11" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="84" t="s">
+      <c r="D11" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="84" t="s">
+      <c r="E11" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="84" t="s">
+      <c r="F11" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="84" t="s">
+      <c r="G11" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="84" t="s">
+      <c r="H11" s="94" t="s">
         <v>13</v>
       </c>
       <c r="I11" s="3"/>
@@ -1562,14 +1572,14 @@
       <c r="Z11" s="3"/>
     </row>
     <row r="12" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A12" s="85"/>
-      <c r="B12" s="85"/>
-      <c r="C12" s="85"/>
-      <c r="D12" s="85"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="85"/>
-      <c r="H12" s="85"/>
+      <c r="A12" s="95"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -1590,20 +1600,20 @@
       <c r="Z12" s="3"/>
     </row>
     <row r="13" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A13" s="33"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="31" t="e">
+      <c r="A13" s="31"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="30" t="e">
         <f>E13/C13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G13" s="31" t="e">
+      <c r="G13" s="30" t="e">
         <f>F13*B13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H13" s="32"/>
+      <c r="H13" s="85"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -1624,20 +1634,20 @@
       <c r="Z13" s="3"/>
     </row>
     <row r="14" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A14" s="33"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="31" t="e">
-        <f t="shared" ref="F14:F43" si="0">E14/C14</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G14" s="31" t="e">
-        <f t="shared" ref="G14:G43" si="1">F14*B14</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H14" s="18"/>
+      <c r="A14" s="31"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="30" t="e">
+        <f t="shared" ref="F14:F40" si="0">E14/C14</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G14" s="30" t="e">
+        <f t="shared" ref="G14:G40" si="1">F14*B14</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H14" s="86"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -1658,20 +1668,20 @@
       <c r="Z14" s="3"/>
     </row>
     <row r="15" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A15" s="33"/>
-      <c r="B15" s="35"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="31" t="e">
+      <c r="A15" s="31"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G15" s="31" t="e">
+      <c r="G15" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H15" s="18"/>
+      <c r="H15" s="86"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -1692,20 +1702,20 @@
       <c r="Z15" s="3"/>
     </row>
     <row r="16" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A16" s="33"/>
-      <c r="B16" s="35"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="31" t="e">
+      <c r="A16" s="31"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G16" s="31" t="e">
+      <c r="G16" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H16" s="18"/>
+      <c r="H16" s="86"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -1726,20 +1736,20 @@
       <c r="Z16" s="3"/>
     </row>
     <row r="17" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A17" s="33"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="31" t="e">
+      <c r="A17" s="31"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G17" s="31" t="e">
+      <c r="G17" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H17" s="18"/>
+      <c r="H17" s="86"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
@@ -1760,20 +1770,20 @@
       <c r="Z17" s="3"/>
     </row>
     <row r="18" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A18" s="33"/>
-      <c r="B18" s="35"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="31" t="e">
+      <c r="A18" s="31"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G18" s="31" t="e">
+      <c r="G18" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H18" s="18"/>
+      <c r="H18" s="86"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
@@ -1794,20 +1804,20 @@
       <c r="Z18" s="3"/>
     </row>
     <row r="19" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A19" s="33"/>
-      <c r="B19" s="35"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="31" t="e">
+      <c r="A19" s="31"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G19" s="31" t="e">
+      <c r="G19" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H19" s="18"/>
+      <c r="H19" s="86"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -1828,20 +1838,20 @@
       <c r="Z19" s="3"/>
     </row>
     <row r="20" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A20" s="33"/>
-      <c r="B20" s="35"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="31" t="e">
+      <c r="A20" s="31"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G20" s="31" t="e">
+      <c r="G20" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H20" s="18"/>
+      <c r="H20" s="86"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
@@ -1862,20 +1872,20 @@
       <c r="Z20" s="3"/>
     </row>
     <row r="21" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A21" s="33"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="31" t="e">
+      <c r="A21" s="31"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G21" s="31" t="e">
+      <c r="G21" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H21" s="18"/>
+      <c r="H21" s="86"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
@@ -1896,20 +1906,20 @@
       <c r="Z21" s="3"/>
     </row>
     <row r="22" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A22" s="33"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="31" t="e">
+      <c r="A22" s="31"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G22" s="31" t="e">
+      <c r="G22" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H22" s="18"/>
+      <c r="H22" s="86"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
@@ -1930,20 +1940,20 @@
       <c r="Z22" s="3"/>
     </row>
     <row r="23" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A23" s="33"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="31" t="e">
+      <c r="A23" s="31"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G23" s="31" t="e">
+      <c r="G23" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H23" s="18"/>
+      <c r="H23" s="86"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
@@ -1964,20 +1974,20 @@
       <c r="Z23" s="3"/>
     </row>
     <row r="24" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A24" s="33"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="31" t="e">
+      <c r="A24" s="31"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G24" s="31" t="e">
+      <c r="G24" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H24" s="19"/>
+      <c r="H24" s="87"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
@@ -1998,20 +2008,20 @@
       <c r="Z24" s="3"/>
     </row>
     <row r="25" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A25" s="41"/>
-      <c r="B25" s="42"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="31" t="e">
+      <c r="A25" s="39"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G25" s="31" t="e">
+      <c r="G25" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H25" s="19"/>
+      <c r="H25" s="87"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
@@ -2032,20 +2042,20 @@
       <c r="Z25" s="3"/>
     </row>
     <row r="26" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A26" s="41"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="31" t="e">
+      <c r="A26" s="39"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G26" s="31" t="e">
+      <c r="G26" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H26" s="19"/>
+      <c r="H26" s="87"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
@@ -2066,20 +2076,20 @@
       <c r="Z26" s="3"/>
     </row>
     <row r="27" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A27" s="41"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="31" t="e">
+      <c r="A27" s="39"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G27" s="31" t="e">
+      <c r="G27" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H27" s="19"/>
+      <c r="H27" s="87"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
@@ -2100,20 +2110,20 @@
       <c r="Z27" s="3"/>
     </row>
     <row r="28" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A28" s="41"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="31" t="e">
+      <c r="A28" s="39"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G28" s="31" t="e">
+      <c r="G28" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H28" s="18"/>
+      <c r="H28" s="86"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
@@ -2134,20 +2144,20 @@
       <c r="Z28" s="3"/>
     </row>
     <row r="29" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A29" s="41"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="31" t="e">
+      <c r="A29" s="39"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G29" s="31" t="e">
+      <c r="G29" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H29" s="19"/>
+      <c r="H29" s="87"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
@@ -2168,20 +2178,20 @@
       <c r="Z29" s="3"/>
     </row>
     <row r="30" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A30" s="41"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="31" t="e">
+      <c r="A30" s="39"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G30" s="31" t="e">
+      <c r="G30" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H30" s="19"/>
+      <c r="H30" s="87"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
@@ -2202,20 +2212,20 @@
       <c r="Z30" s="3"/>
     </row>
     <row r="31" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A31" s="41"/>
-      <c r="B31" s="42"/>
-      <c r="C31" s="36"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="31" t="e">
+      <c r="A31" s="39"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G31" s="31" t="e">
+      <c r="G31" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H31" s="19"/>
+      <c r="H31" s="87"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
@@ -2236,20 +2246,20 @@
       <c r="Z31" s="3"/>
     </row>
     <row r="32" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A32" s="41"/>
-      <c r="B32" s="42"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="31" t="e">
+      <c r="A32" s="39"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G32" s="31" t="e">
+      <c r="G32" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H32" s="19"/>
+      <c r="H32" s="87"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
@@ -2270,20 +2280,20 @@
       <c r="Z32" s="3"/>
     </row>
     <row r="33" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A33" s="41"/>
-      <c r="B33" s="42"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="31" t="e">
+      <c r="A33" s="39"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G33" s="31" t="e">
+      <c r="G33" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H33" s="19"/>
+      <c r="H33" s="87"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
@@ -2304,20 +2314,20 @@
       <c r="Z33" s="3"/>
     </row>
     <row r="34" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A34" s="41"/>
-      <c r="B34" s="42"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="31" t="e">
+      <c r="A34" s="39"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G34" s="31" t="e">
+      <c r="G34" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H34" s="19"/>
+      <c r="H34" s="87"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
@@ -2338,20 +2348,20 @@
       <c r="Z34" s="3"/>
     </row>
     <row r="35" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A35" s="41"/>
-      <c r="B35" s="42"/>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="31" t="e">
+      <c r="A35" s="39"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G35" s="31" t="e">
+      <c r="G35" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H35" s="19"/>
+      <c r="H35" s="87"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
@@ -2372,20 +2382,20 @@
       <c r="Z35" s="3"/>
     </row>
     <row r="36" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A36" s="41"/>
-      <c r="B36" s="42"/>
-      <c r="C36" s="43"/>
-      <c r="D36" s="43"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="31" t="e">
+      <c r="A36" s="39"/>
+      <c r="B36" s="40"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G36" s="31" t="e">
+      <c r="G36" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H36" s="19"/>
+      <c r="H36" s="87"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
@@ -2406,20 +2416,20 @@
       <c r="Z36" s="3"/>
     </row>
     <row r="37" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A37" s="34"/>
+      <c r="A37" s="32"/>
       <c r="B37" s="5"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
-      <c r="F37" s="31" t="e">
+      <c r="F37" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G37" s="31" t="e">
+      <c r="G37" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H37" s="19"/>
+      <c r="H37" s="87"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
@@ -2440,20 +2450,20 @@
       <c r="Z37" s="3"/>
     </row>
     <row r="38" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A38" s="34"/>
+      <c r="A38" s="32"/>
       <c r="B38" s="5"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
-      <c r="F38" s="31" t="e">
+      <c r="F38" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G38" s="31" t="e">
+      <c r="G38" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H38" s="19"/>
+      <c r="H38" s="87"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
@@ -2474,20 +2484,20 @@
       <c r="Z38" s="3"/>
     </row>
     <row r="39" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A39" s="34"/>
+      <c r="A39" s="32"/>
       <c r="B39" s="5"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
-      <c r="F39" s="31" t="e">
+      <c r="F39" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G39" s="31" t="e">
+      <c r="G39" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H39" s="19"/>
+      <c r="H39" s="87"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
@@ -2508,20 +2518,20 @@
       <c r="Z39" s="3"/>
     </row>
     <row r="40" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A40" s="34"/>
+      <c r="A40" s="32"/>
       <c r="B40" s="5"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
-      <c r="F40" s="31" t="e">
+      <c r="F40" s="30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G40" s="31" t="e">
+      <c r="G40" s="30" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H40" s="19"/>
+      <c r="H40" s="87"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
@@ -2542,14 +2552,14 @@
       <c r="Z40" s="3"/>
     </row>
     <row r="41" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A41" s="34"/>
+      <c r="A41" s="32"/>
       <c r="B41" s="4"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="19"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="18"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
@@ -2570,14 +2580,14 @@
       <c r="Z41" s="3"/>
     </row>
     <row r="42" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A42" s="34"/>
+      <c r="A42" s="32"/>
       <c r="B42" s="4"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="19"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="18"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
@@ -2598,14 +2608,14 @@
       <c r="Z42" s="3"/>
     </row>
     <row r="43" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A43" s="34"/>
+      <c r="A43" s="32"/>
       <c r="B43" s="4"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="19"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="18"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
@@ -2627,711 +2637,706 @@
     </row>
     <row r="44" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
       <c r="A44" s="15"/>
-      <c r="B44" s="49"/>
-      <c r="C44" s="49"/>
-      <c r="D44" s="49"/>
-      <c r="E44" s="49"/>
-      <c r="F44" s="49"/>
+      <c r="B44" s="47"/>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="47"/>
       <c r="G44" s="7"/>
-      <c r="H44" s="20"/>
+      <c r="H44" s="19"/>
     </row>
     <row r="45" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A45" s="23" t="s">
+      <c r="A45" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B45" s="24"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="69" t="s">
+      <c r="B45" s="23"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="G45" s="70" t="e">
+      <c r="G45" s="68" t="e">
         <f>SUM(G13:G43)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H45" s="71" t="s">
+      <c r="H45" s="69" t="s">
         <v>16</v>
       </c>
       <c r="K45" s="10"/>
     </row>
     <row r="46" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A46" s="44"/>
-      <c r="B46" s="64"/>
-      <c r="C46" s="64"/>
-      <c r="D46" s="64"/>
-      <c r="E46" s="45"/>
-      <c r="F46" s="72" t="s">
+      <c r="A46" s="42"/>
+      <c r="B46" s="62"/>
+      <c r="C46" s="62"/>
+      <c r="D46" s="62"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="70" t="s">
         <v>8</v>
       </c>
       <c r="G46" s="9"/>
-      <c r="H46" s="21"/>
+      <c r="H46" s="20"/>
       <c r="K46" s="10"/>
     </row>
     <row r="47" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A47" s="44"/>
-      <c r="B47" s="64"/>
-      <c r="C47" s="64"/>
-      <c r="D47" s="64"/>
-      <c r="E47" s="45"/>
-      <c r="F47" s="72" t="s">
+      <c r="A47" s="42"/>
+      <c r="B47" s="62"/>
+      <c r="C47" s="62"/>
+      <c r="D47" s="62"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="G47" s="26" t="e">
+      <c r="G47" s="25" t="e">
         <f>SUM(G45,G46)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H47" s="89"/>
+      <c r="H47" s="73"/>
       <c r="K47" s="11"/>
     </row>
     <row r="48" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A48" s="44"/>
-      <c r="B48" s="64"/>
-      <c r="C48" s="64"/>
-      <c r="D48" s="64"/>
-      <c r="E48" s="45"/>
-      <c r="F48" s="73" t="s">
+      <c r="A48" s="42"/>
+      <c r="B48" s="62"/>
+      <c r="C48" s="62"/>
+      <c r="D48" s="62"/>
+      <c r="E48" s="43"/>
+      <c r="F48" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="G48" s="56"/>
+      <c r="G48" s="54"/>
       <c r="H48" s="14"/>
       <c r="K48" s="10"/>
     </row>
     <row r="49" spans="1:10" ht="24.6" customHeight="1">
-      <c r="A49" s="44"/>
-      <c r="B49" s="64"/>
-      <c r="C49" s="64"/>
-      <c r="D49" s="64"/>
-      <c r="E49" s="45"/>
-      <c r="F49" s="72" t="s">
+      <c r="A49" s="42"/>
+      <c r="B49" s="62"/>
+      <c r="C49" s="62"/>
+      <c r="D49" s="62"/>
+      <c r="E49" s="43"/>
+      <c r="F49" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="G49" s="27" t="e">
+      <c r="G49" s="26" t="e">
         <f>G47/G48</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H49" s="20" t="s">
+      <c r="H49" s="19" t="s">
         <v>17</v>
       </c>
       <c r="J49" s="8"/>
     </row>
     <row r="50" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A50" s="44"/>
-      <c r="B50" s="64"/>
-      <c r="C50" s="64"/>
-      <c r="D50" s="64"/>
-      <c r="E50" s="45"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="28"/>
-      <c r="H50" s="30"/>
+      <c r="A50" s="42"/>
+      <c r="B50" s="62"/>
+      <c r="C50" s="62"/>
+      <c r="D50" s="62"/>
+      <c r="E50" s="43"/>
+      <c r="F50" s="72"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="29"/>
       <c r="I50" s="8"/>
       <c r="J50" s="8"/>
     </row>
     <row r="51" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A51" s="44"/>
-      <c r="B51" s="64"/>
-      <c r="C51" s="64"/>
-      <c r="D51" s="64"/>
-      <c r="E51" s="45"/>
-      <c r="F51" s="73" t="s">
+      <c r="A51" s="42"/>
+      <c r="B51" s="62"/>
+      <c r="C51" s="62"/>
+      <c r="D51" s="62"/>
+      <c r="E51" s="43"/>
+      <c r="F51" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="G51" s="29" t="e">
+      <c r="G51" s="28" t="e">
         <f>G47/F8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H51" s="89"/>
+      <c r="H51" s="73"/>
       <c r="I51" s="8"/>
       <c r="J51" s="8"/>
     </row>
     <row r="52" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A52" s="46"/>
-      <c r="B52" s="47"/>
-      <c r="C52" s="47"/>
-      <c r="D52" s="47"/>
-      <c r="E52" s="48"/>
-      <c r="F52" s="39" t="s">
+      <c r="A52" s="44"/>
+      <c r="B52" s="45"/>
+      <c r="C52" s="45"/>
+      <c r="D52" s="45"/>
+      <c r="E52" s="46"/>
+      <c r="F52" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="G52" s="40" t="e">
+      <c r="G52" s="38" t="e">
         <f>G48/F8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H52" s="22"/>
+      <c r="H52" s="21"/>
     </row>
     <row r="53" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A53" s="65"/>
-      <c r="B53" s="66"/>
-      <c r="C53" s="66"/>
-      <c r="D53" s="66"/>
-      <c r="E53" s="67"/>
-      <c r="F53" s="67"/>
-      <c r="G53" s="67"/>
-      <c r="H53" s="68"/>
+      <c r="A53" s="63"/>
+      <c r="B53" s="64"/>
+      <c r="C53" s="64"/>
+      <c r="D53" s="64"/>
+      <c r="E53" s="65"/>
+      <c r="F53" s="65"/>
+      <c r="G53" s="65"/>
+      <c r="H53" s="66"/>
     </row>
     <row r="54" spans="1:10" ht="24.6" customHeight="1">
-      <c r="A54" s="60" t="s">
+      <c r="A54" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B54" s="59"/>
-      <c r="C54" s="59"/>
-      <c r="D54" s="59"/>
-      <c r="E54" s="24"/>
-      <c r="F54" s="24"/>
-      <c r="G54" s="24"/>
-      <c r="H54" s="25"/>
+      <c r="B54" s="57"/>
+      <c r="C54" s="57"/>
+      <c r="D54" s="57"/>
+      <c r="E54" s="23"/>
+      <c r="F54" s="23"/>
+      <c r="G54" s="23"/>
+      <c r="H54" s="24"/>
     </row>
     <row r="55" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A55" s="79"/>
-      <c r="B55" s="80"/>
-      <c r="C55" s="80"/>
-      <c r="D55" s="80"/>
-      <c r="E55" s="49"/>
-      <c r="F55" s="50"/>
-      <c r="G55" s="50"/>
+      <c r="A55" s="88"/>
+      <c r="B55" s="89"/>
+      <c r="C55" s="89"/>
+      <c r="D55" s="89"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="48"/>
+      <c r="G55" s="48"/>
       <c r="H55" s="14"/>
     </row>
     <row r="56" spans="1:10" ht="24.6" customHeight="1">
       <c r="A56" s="15"/>
-      <c r="B56" s="49"/>
-      <c r="C56" s="49"/>
-      <c r="D56" s="49"/>
-      <c r="E56" s="49"/>
-      <c r="F56" s="50"/>
-      <c r="G56" s="50"/>
+      <c r="B56" s="47"/>
+      <c r="C56" s="47"/>
+      <c r="D56" s="47"/>
+      <c r="E56" s="47"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="48"/>
       <c r="H56" s="14"/>
     </row>
     <row r="57" spans="1:10" ht="24.6" customHeight="1">
-      <c r="A57" s="37" t="s">
+      <c r="A57" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B57" s="49"/>
-      <c r="C57" s="49"/>
-      <c r="D57" s="49"/>
-      <c r="E57" s="49"/>
-      <c r="F57" s="49"/>
-      <c r="G57" s="50"/>
+      <c r="B57" s="47"/>
+      <c r="C57" s="47"/>
+      <c r="D57" s="47"/>
+      <c r="E57" s="47"/>
+      <c r="F57" s="47"/>
+      <c r="G57" s="48"/>
       <c r="H57" s="14"/>
     </row>
     <row r="58" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A58" s="79"/>
-      <c r="B58" s="80"/>
-      <c r="C58" s="80"/>
-      <c r="D58" s="80"/>
-      <c r="E58" s="51"/>
-      <c r="F58" s="49"/>
-      <c r="G58" s="50"/>
+      <c r="A58" s="88"/>
+      <c r="B58" s="89"/>
+      <c r="C58" s="89"/>
+      <c r="D58" s="89"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="47"/>
+      <c r="G58" s="48"/>
       <c r="H58" s="16"/>
     </row>
     <row r="59" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A59" s="52"/>
-      <c r="B59" s="53"/>
-      <c r="C59" s="78"/>
-      <c r="D59" s="78"/>
-      <c r="E59" s="53"/>
-      <c r="F59" s="54"/>
-      <c r="G59" s="54"/>
-      <c r="H59" s="55"/>
+      <c r="A59" s="50"/>
+      <c r="B59" s="51"/>
+      <c r="C59" s="93"/>
+      <c r="D59" s="93"/>
+      <c r="E59" s="51"/>
+      <c r="F59" s="52"/>
+      <c r="G59" s="52"/>
+      <c r="H59" s="53"/>
     </row>
     <row r="60" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A60" s="75" t="s">
+      <c r="A60" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="B60" s="76"/>
-      <c r="C60" s="76"/>
-      <c r="D60" s="76"/>
-      <c r="E60" s="76"/>
-      <c r="F60" s="76"/>
-      <c r="G60" s="76"/>
-      <c r="H60" s="77"/>
+      <c r="B60" s="91"/>
+      <c r="C60" s="91"/>
+      <c r="D60" s="91"/>
+      <c r="E60" s="91"/>
+      <c r="F60" s="91"/>
+      <c r="G60" s="91"/>
+      <c r="H60" s="92"/>
     </row>
     <row r="61" spans="1:10" ht="24.6" customHeight="1">
-      <c r="A61" s="90"/>
-      <c r="B61" s="91"/>
-      <c r="C61" s="91"/>
-      <c r="D61" s="91"/>
-      <c r="E61" s="91"/>
-      <c r="F61" s="91"/>
-      <c r="G61" s="91"/>
-      <c r="H61" s="92"/>
+      <c r="A61" s="76"/>
+      <c r="B61" s="74"/>
+      <c r="C61" s="74"/>
+      <c r="D61" s="74"/>
+      <c r="E61" s="74"/>
+      <c r="F61" s="74"/>
+      <c r="G61" s="74"/>
+      <c r="H61" s="75"/>
     </row>
     <row r="62" spans="1:10" ht="24.6" customHeight="1">
-      <c r="A62" s="90"/>
-      <c r="B62" s="91"/>
-      <c r="C62" s="91"/>
-      <c r="D62" s="91"/>
-      <c r="E62" s="91"/>
-      <c r="F62" s="91"/>
-      <c r="G62" s="91"/>
-      <c r="H62" s="92"/>
+      <c r="A62" s="76"/>
+      <c r="B62" s="74"/>
+      <c r="C62" s="74"/>
+      <c r="D62" s="74"/>
+      <c r="E62" s="74"/>
+      <c r="F62" s="74"/>
+      <c r="G62" s="74"/>
+      <c r="H62" s="75"/>
     </row>
     <row r="63" spans="1:10" ht="24.6" customHeight="1">
-      <c r="A63" s="90"/>
-      <c r="B63" s="91"/>
-      <c r="C63" s="91"/>
-      <c r="D63" s="91"/>
-      <c r="E63" s="91"/>
-      <c r="F63" s="91"/>
-      <c r="G63" s="91"/>
-      <c r="H63" s="92"/>
+      <c r="A63" s="76"/>
+      <c r="B63" s="74"/>
+      <c r="C63" s="74"/>
+      <c r="D63" s="74"/>
+      <c r="E63" s="74"/>
+      <c r="F63" s="74"/>
+      <c r="G63" s="74"/>
+      <c r="H63" s="75"/>
     </row>
     <row r="64" spans="1:10" ht="24.6" customHeight="1">
-      <c r="A64" s="93"/>
-      <c r="B64" s="94"/>
-      <c r="C64" s="94"/>
-      <c r="D64" s="94"/>
-      <c r="E64" s="94"/>
-      <c r="F64" s="94"/>
-      <c r="G64" s="94"/>
-      <c r="H64" s="95"/>
+      <c r="A64" s="76"/>
+      <c r="B64" s="77"/>
+      <c r="C64" s="77"/>
+      <c r="D64" s="77"/>
+      <c r="E64" s="77"/>
+      <c r="F64" s="77"/>
+      <c r="G64" s="77"/>
+      <c r="H64" s="78"/>
     </row>
     <row r="65" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A65" s="93"/>
-      <c r="B65" s="94"/>
-      <c r="C65" s="94"/>
-      <c r="D65" s="94"/>
-      <c r="E65" s="94"/>
-      <c r="F65" s="94"/>
-      <c r="G65" s="94"/>
-      <c r="H65" s="95"/>
+      <c r="A65" s="76"/>
+      <c r="B65" s="77"/>
+      <c r="C65" s="77"/>
+      <c r="D65" s="77"/>
+      <c r="E65" s="77"/>
+      <c r="F65" s="77"/>
+      <c r="G65" s="77"/>
+      <c r="H65" s="78"/>
     </row>
     <row r="66" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A66" s="93"/>
-      <c r="B66" s="94"/>
-      <c r="C66" s="94"/>
-      <c r="D66" s="94"/>
-      <c r="E66" s="94"/>
-      <c r="F66" s="94"/>
-      <c r="G66" s="94"/>
-      <c r="H66" s="95"/>
+      <c r="A66" s="76"/>
+      <c r="B66" s="77"/>
+      <c r="C66" s="77"/>
+      <c r="D66" s="77"/>
+      <c r="E66" s="77"/>
+      <c r="F66" s="77"/>
+      <c r="G66" s="77"/>
+      <c r="H66" s="78"/>
     </row>
     <row r="67" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A67" s="93"/>
-      <c r="B67" s="94"/>
-      <c r="C67" s="94"/>
-      <c r="D67" s="94"/>
-      <c r="E67" s="94"/>
-      <c r="F67" s="94"/>
-      <c r="G67" s="94"/>
-      <c r="H67" s="95"/>
+      <c r="A67" s="76"/>
+      <c r="B67" s="77"/>
+      <c r="C67" s="77"/>
+      <c r="D67" s="77"/>
+      <c r="E67" s="77"/>
+      <c r="F67" s="77"/>
+      <c r="G67" s="77"/>
+      <c r="H67" s="78"/>
     </row>
     <row r="68" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A68" s="93"/>
-      <c r="B68" s="94"/>
-      <c r="C68" s="94"/>
-      <c r="D68" s="94"/>
-      <c r="E68" s="94"/>
-      <c r="F68" s="94"/>
-      <c r="G68" s="94"/>
-      <c r="H68" s="95"/>
+      <c r="A68" s="76"/>
+      <c r="B68" s="77"/>
+      <c r="C68" s="77"/>
+      <c r="D68" s="77"/>
+      <c r="E68" s="77"/>
+      <c r="F68" s="77"/>
+      <c r="G68" s="77"/>
+      <c r="H68" s="78"/>
     </row>
     <row r="69" spans="1:8" ht="27.6" customHeight="1">
-      <c r="A69" s="93"/>
-      <c r="B69" s="94"/>
-      <c r="C69" s="94"/>
-      <c r="D69" s="94"/>
-      <c r="E69" s="94"/>
-      <c r="F69" s="94"/>
-      <c r="G69" s="94"/>
-      <c r="H69" s="95"/>
+      <c r="A69" s="76"/>
+      <c r="B69" s="77"/>
+      <c r="C69" s="77"/>
+      <c r="D69" s="77"/>
+      <c r="E69" s="77"/>
+      <c r="F69" s="77"/>
+      <c r="G69" s="77"/>
+      <c r="H69" s="78"/>
     </row>
     <row r="70" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A70" s="93"/>
-      <c r="B70" s="94"/>
-      <c r="C70" s="94"/>
-      <c r="D70" s="94"/>
-      <c r="E70" s="94"/>
-      <c r="F70" s="94"/>
-      <c r="G70" s="94"/>
-      <c r="H70" s="95"/>
+      <c r="A70" s="76"/>
+      <c r="B70" s="77"/>
+      <c r="C70" s="77"/>
+      <c r="D70" s="77"/>
+      <c r="E70" s="77"/>
+      <c r="F70" s="77"/>
+      <c r="G70" s="77"/>
+      <c r="H70" s="78"/>
     </row>
     <row r="71" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A71" s="93"/>
-      <c r="B71" s="94"/>
-      <c r="C71" s="94"/>
-      <c r="D71" s="94"/>
-      <c r="E71" s="94"/>
-      <c r="F71" s="94"/>
-      <c r="G71" s="94"/>
-      <c r="H71" s="95"/>
+      <c r="A71" s="76"/>
+      <c r="B71" s="77"/>
+      <c r="C71" s="77"/>
+      <c r="D71" s="77"/>
+      <c r="E71" s="77"/>
+      <c r="F71" s="77"/>
+      <c r="G71" s="77"/>
+      <c r="H71" s="78"/>
     </row>
     <row r="72" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A72" s="93"/>
-      <c r="B72" s="94"/>
-      <c r="C72" s="94"/>
-      <c r="D72" s="94"/>
-      <c r="E72" s="94"/>
-      <c r="F72" s="94"/>
-      <c r="G72" s="94"/>
-      <c r="H72" s="95"/>
+      <c r="A72" s="76"/>
+      <c r="B72" s="77"/>
+      <c r="C72" s="77"/>
+      <c r="D72" s="77"/>
+      <c r="E72" s="77"/>
+      <c r="F72" s="77"/>
+      <c r="G72" s="77"/>
+      <c r="H72" s="78"/>
     </row>
     <row r="73" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A73" s="93"/>
-      <c r="B73" s="94"/>
-      <c r="C73" s="94"/>
-      <c r="D73" s="94"/>
-      <c r="E73" s="94"/>
-      <c r="F73" s="94"/>
-      <c r="G73" s="94"/>
-      <c r="H73" s="95"/>
+      <c r="A73" s="76"/>
+      <c r="B73" s="77"/>
+      <c r="C73" s="77"/>
+      <c r="D73" s="77"/>
+      <c r="E73" s="77"/>
+      <c r="F73" s="77"/>
+      <c r="G73" s="77"/>
+      <c r="H73" s="78"/>
     </row>
     <row r="74" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A74" s="93"/>
-      <c r="B74" s="94"/>
-      <c r="C74" s="94"/>
-      <c r="D74" s="94"/>
-      <c r="E74" s="94"/>
-      <c r="F74" s="94"/>
-      <c r="G74" s="94"/>
-      <c r="H74" s="95"/>
+      <c r="A74" s="76"/>
+      <c r="B74" s="77"/>
+      <c r="C74" s="77"/>
+      <c r="D74" s="77"/>
+      <c r="E74" s="77"/>
+      <c r="F74" s="77"/>
+      <c r="G74" s="77"/>
+      <c r="H74" s="78"/>
     </row>
     <row r="75" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A75" s="93"/>
-      <c r="B75" s="94"/>
-      <c r="C75" s="94"/>
-      <c r="D75" s="94"/>
-      <c r="E75" s="94"/>
-      <c r="F75" s="94"/>
-      <c r="G75" s="94"/>
-      <c r="H75" s="95"/>
+      <c r="A75" s="76"/>
+      <c r="B75" s="77"/>
+      <c r="C75" s="77"/>
+      <c r="D75" s="77"/>
+      <c r="E75" s="77"/>
+      <c r="F75" s="77"/>
+      <c r="G75" s="77"/>
+      <c r="H75" s="78"/>
     </row>
     <row r="76" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A76" s="93"/>
-      <c r="B76" s="94"/>
-      <c r="C76" s="94"/>
-      <c r="D76" s="94"/>
-      <c r="E76" s="94"/>
-      <c r="F76" s="94"/>
-      <c r="G76" s="94"/>
-      <c r="H76" s="95"/>
+      <c r="A76" s="76"/>
+      <c r="B76" s="77"/>
+      <c r="C76" s="77"/>
+      <c r="D76" s="77"/>
+      <c r="E76" s="77"/>
+      <c r="F76" s="77"/>
+      <c r="G76" s="77"/>
+      <c r="H76" s="78"/>
     </row>
     <row r="77" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A77" s="93"/>
-      <c r="B77" s="94"/>
-      <c r="C77" s="94"/>
-      <c r="D77" s="94"/>
-      <c r="E77" s="94"/>
-      <c r="F77" s="94"/>
-      <c r="G77" s="94"/>
-      <c r="H77" s="95"/>
+      <c r="A77" s="76"/>
+      <c r="B77" s="77"/>
+      <c r="C77" s="77"/>
+      <c r="D77" s="77"/>
+      <c r="E77" s="77"/>
+      <c r="F77" s="77"/>
+      <c r="G77" s="77"/>
+      <c r="H77" s="78"/>
     </row>
     <row r="78" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A78" s="93"/>
-      <c r="B78" s="94"/>
-      <c r="C78" s="94"/>
-      <c r="D78" s="94"/>
-      <c r="E78" s="94"/>
-      <c r="F78" s="94"/>
-      <c r="G78" s="94"/>
-      <c r="H78" s="95"/>
+      <c r="A78" s="76"/>
+      <c r="B78" s="77"/>
+      <c r="C78" s="77"/>
+      <c r="D78" s="77"/>
+      <c r="E78" s="77"/>
+      <c r="F78" s="77"/>
+      <c r="G78" s="77"/>
+      <c r="H78" s="78"/>
     </row>
     <row r="79" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A79" s="93"/>
-      <c r="B79" s="94"/>
-      <c r="C79" s="94"/>
-      <c r="D79" s="94"/>
-      <c r="E79" s="94"/>
-      <c r="F79" s="94"/>
-      <c r="G79" s="94"/>
-      <c r="H79" s="95"/>
+      <c r="A79" s="76"/>
+      <c r="B79" s="77"/>
+      <c r="C79" s="77"/>
+      <c r="D79" s="77"/>
+      <c r="E79" s="77"/>
+      <c r="F79" s="77"/>
+      <c r="G79" s="77"/>
+      <c r="H79" s="78"/>
     </row>
     <row r="80" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A80" s="93"/>
-      <c r="B80" s="94"/>
-      <c r="C80" s="94"/>
-      <c r="D80" s="94"/>
-      <c r="E80" s="94"/>
-      <c r="F80" s="94"/>
-      <c r="G80" s="94"/>
-      <c r="H80" s="95"/>
+      <c r="A80" s="76"/>
+      <c r="B80" s="77"/>
+      <c r="C80" s="77"/>
+      <c r="D80" s="77"/>
+      <c r="E80" s="77"/>
+      <c r="F80" s="77"/>
+      <c r="G80" s="77"/>
+      <c r="H80" s="78"/>
     </row>
     <row r="81" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A81" s="93"/>
-      <c r="B81" s="94"/>
-      <c r="C81" s="94"/>
-      <c r="D81" s="94"/>
-      <c r="E81" s="94"/>
-      <c r="F81" s="94"/>
-      <c r="G81" s="94"/>
-      <c r="H81" s="95"/>
+      <c r="A81" s="76"/>
+      <c r="B81" s="77"/>
+      <c r="C81" s="77"/>
+      <c r="D81" s="77"/>
+      <c r="E81" s="77"/>
+      <c r="F81" s="77"/>
+      <c r="G81" s="77"/>
+      <c r="H81" s="78"/>
     </row>
     <row r="82" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A82" s="93"/>
-      <c r="B82" s="94"/>
-      <c r="C82" s="94"/>
-      <c r="D82" s="94"/>
-      <c r="E82" s="94"/>
-      <c r="F82" s="94"/>
-      <c r="G82" s="94"/>
-      <c r="H82" s="95"/>
+      <c r="A82" s="76"/>
+      <c r="B82" s="77"/>
+      <c r="C82" s="77"/>
+      <c r="D82" s="77"/>
+      <c r="E82" s="77"/>
+      <c r="F82" s="77"/>
+      <c r="G82" s="77"/>
+      <c r="H82" s="78"/>
     </row>
     <row r="83" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A83" s="93"/>
-      <c r="B83" s="94"/>
-      <c r="C83" s="94"/>
-      <c r="D83" s="94"/>
-      <c r="E83" s="94"/>
-      <c r="F83" s="94"/>
-      <c r="G83" s="94"/>
-      <c r="H83" s="95"/>
+      <c r="A83" s="76"/>
+      <c r="B83" s="77"/>
+      <c r="C83" s="77"/>
+      <c r="D83" s="77"/>
+      <c r="E83" s="77"/>
+      <c r="F83" s="77"/>
+      <c r="G83" s="77"/>
+      <c r="H83" s="78"/>
     </row>
     <row r="84" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A84" s="93"/>
-      <c r="B84" s="94"/>
-      <c r="C84" s="94"/>
-      <c r="D84" s="94"/>
-      <c r="E84" s="94"/>
-      <c r="F84" s="94"/>
-      <c r="G84" s="94"/>
-      <c r="H84" s="95"/>
+      <c r="A84" s="76"/>
+      <c r="B84" s="77"/>
+      <c r="C84" s="77"/>
+      <c r="D84" s="77"/>
+      <c r="E84" s="77"/>
+      <c r="F84" s="77"/>
+      <c r="G84" s="77"/>
+      <c r="H84" s="78"/>
     </row>
     <row r="85" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A85" s="93"/>
-      <c r="B85" s="94"/>
-      <c r="C85" s="94"/>
-      <c r="D85" s="94"/>
-      <c r="E85" s="94"/>
-      <c r="F85" s="94"/>
-      <c r="G85" s="94"/>
-      <c r="H85" s="95"/>
+      <c r="A85" s="76"/>
+      <c r="B85" s="77"/>
+      <c r="C85" s="77"/>
+      <c r="D85" s="77"/>
+      <c r="E85" s="77"/>
+      <c r="F85" s="77"/>
+      <c r="G85" s="77"/>
+      <c r="H85" s="78"/>
     </row>
     <row r="86" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A86" s="93"/>
-      <c r="B86" s="94"/>
-      <c r="C86" s="94"/>
-      <c r="D86" s="94"/>
-      <c r="E86" s="94"/>
-      <c r="F86" s="94"/>
-      <c r="G86" s="94"/>
-      <c r="H86" s="95"/>
+      <c r="A86" s="76"/>
+      <c r="B86" s="77"/>
+      <c r="C86" s="77"/>
+      <c r="D86" s="77"/>
+      <c r="E86" s="77"/>
+      <c r="F86" s="77"/>
+      <c r="G86" s="77"/>
+      <c r="H86" s="78"/>
     </row>
     <row r="87" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A87" s="93"/>
-      <c r="B87" s="94"/>
-      <c r="C87" s="94"/>
-      <c r="D87" s="94"/>
-      <c r="E87" s="94"/>
-      <c r="F87" s="94"/>
-      <c r="G87" s="94"/>
-      <c r="H87" s="95"/>
+      <c r="A87" s="76"/>
+      <c r="B87" s="77"/>
+      <c r="C87" s="77"/>
+      <c r="D87" s="77"/>
+      <c r="E87" s="77"/>
+      <c r="F87" s="77"/>
+      <c r="G87" s="77"/>
+      <c r="H87" s="78"/>
     </row>
     <row r="88" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A88" s="93"/>
-      <c r="B88" s="94"/>
-      <c r="C88" s="94"/>
-      <c r="D88" s="94"/>
-      <c r="E88" s="94"/>
-      <c r="F88" s="94"/>
-      <c r="G88" s="94"/>
-      <c r="H88" s="95"/>
+      <c r="A88" s="76"/>
+      <c r="B88" s="77"/>
+      <c r="C88" s="77"/>
+      <c r="D88" s="77"/>
+      <c r="E88" s="77"/>
+      <c r="F88" s="77"/>
+      <c r="G88" s="77"/>
+      <c r="H88" s="78"/>
     </row>
     <row r="89" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A89" s="93"/>
-      <c r="B89" s="94"/>
-      <c r="C89" s="94"/>
-      <c r="D89" s="94"/>
-      <c r="E89" s="94"/>
-      <c r="F89" s="94"/>
-      <c r="G89" s="94"/>
-      <c r="H89" s="95"/>
+      <c r="A89" s="76"/>
+      <c r="B89" s="77"/>
+      <c r="C89" s="77"/>
+      <c r="D89" s="77"/>
+      <c r="E89" s="77"/>
+      <c r="F89" s="77"/>
+      <c r="G89" s="77"/>
+      <c r="H89" s="78"/>
     </row>
     <row r="90" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A90" s="93"/>
-      <c r="B90" s="94"/>
-      <c r="C90" s="94"/>
-      <c r="D90" s="94"/>
-      <c r="E90" s="94"/>
-      <c r="F90" s="94"/>
-      <c r="G90" s="94"/>
-      <c r="H90" s="95"/>
+      <c r="A90" s="76"/>
+      <c r="B90" s="77"/>
+      <c r="C90" s="77"/>
+      <c r="D90" s="77"/>
+      <c r="E90" s="77"/>
+      <c r="F90" s="77"/>
+      <c r="G90" s="77"/>
+      <c r="H90" s="78"/>
     </row>
     <row r="91" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A91" s="93"/>
-      <c r="B91" s="94"/>
-      <c r="C91" s="94"/>
-      <c r="D91" s="94"/>
-      <c r="E91" s="94"/>
-      <c r="F91" s="94"/>
-      <c r="G91" s="94"/>
-      <c r="H91" s="95"/>
+      <c r="A91" s="76"/>
+      <c r="B91" s="77"/>
+      <c r="C91" s="77"/>
+      <c r="D91" s="77"/>
+      <c r="E91" s="77"/>
+      <c r="F91" s="77"/>
+      <c r="G91" s="77"/>
+      <c r="H91" s="78"/>
     </row>
     <row r="92" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A92" s="93"/>
-      <c r="B92" s="94"/>
-      <c r="C92" s="94"/>
-      <c r="D92" s="94"/>
-      <c r="E92" s="94"/>
-      <c r="F92" s="94"/>
-      <c r="G92" s="94"/>
-      <c r="H92" s="95"/>
+      <c r="A92" s="76"/>
+      <c r="B92" s="77"/>
+      <c r="C92" s="77"/>
+      <c r="D92" s="77"/>
+      <c r="E92" s="77"/>
+      <c r="F92" s="77"/>
+      <c r="G92" s="77"/>
+      <c r="H92" s="78"/>
     </row>
     <row r="93" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A93" s="93"/>
-      <c r="B93" s="94"/>
-      <c r="C93" s="94"/>
-      <c r="D93" s="94"/>
-      <c r="E93" s="94"/>
-      <c r="F93" s="94"/>
-      <c r="G93" s="94"/>
-      <c r="H93" s="95"/>
+      <c r="A93" s="76"/>
+      <c r="B93" s="77"/>
+      <c r="C93" s="77"/>
+      <c r="D93" s="77"/>
+      <c r="E93" s="77"/>
+      <c r="F93" s="77"/>
+      <c r="G93" s="77"/>
+      <c r="H93" s="78"/>
     </row>
     <row r="94" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A94" s="93"/>
-      <c r="B94" s="94"/>
-      <c r="C94" s="94"/>
-      <c r="D94" s="94"/>
-      <c r="E94" s="94"/>
-      <c r="F94" s="94"/>
-      <c r="G94" s="94"/>
-      <c r="H94" s="95"/>
+      <c r="A94" s="76"/>
+      <c r="B94" s="77"/>
+      <c r="C94" s="77"/>
+      <c r="D94" s="77"/>
+      <c r="E94" s="77"/>
+      <c r="F94" s="77"/>
+      <c r="G94" s="77"/>
+      <c r="H94" s="78"/>
     </row>
     <row r="95" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A95" s="93"/>
-      <c r="B95" s="94"/>
-      <c r="C95" s="94"/>
-      <c r="D95" s="94"/>
-      <c r="E95" s="94"/>
-      <c r="F95" s="94"/>
-      <c r="G95" s="94"/>
-      <c r="H95" s="95"/>
+      <c r="A95" s="76"/>
+      <c r="B95" s="77"/>
+      <c r="C95" s="77"/>
+      <c r="D95" s="77"/>
+      <c r="E95" s="77"/>
+      <c r="F95" s="77"/>
+      <c r="G95" s="77"/>
+      <c r="H95" s="78"/>
     </row>
     <row r="96" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A96" s="93"/>
-      <c r="B96" s="94"/>
-      <c r="C96" s="94"/>
-      <c r="D96" s="94"/>
-      <c r="E96" s="94"/>
-      <c r="F96" s="94"/>
-      <c r="G96" s="94"/>
-      <c r="H96" s="95"/>
+      <c r="A96" s="76"/>
+      <c r="B96" s="77"/>
+      <c r="C96" s="77"/>
+      <c r="D96" s="77"/>
+      <c r="E96" s="77"/>
+      <c r="F96" s="77"/>
+      <c r="G96" s="77"/>
+      <c r="H96" s="78"/>
     </row>
     <row r="97" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A97" s="93"/>
-      <c r="B97" s="94"/>
-      <c r="C97" s="94"/>
-      <c r="D97" s="94"/>
-      <c r="E97" s="94"/>
-      <c r="F97" s="94"/>
-      <c r="G97" s="94"/>
-      <c r="H97" s="95"/>
+      <c r="A97" s="76"/>
+      <c r="B97" s="77"/>
+      <c r="C97" s="77"/>
+      <c r="D97" s="77"/>
+      <c r="E97" s="77"/>
+      <c r="F97" s="77"/>
+      <c r="G97" s="77"/>
+      <c r="H97" s="78"/>
     </row>
     <row r="98" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A98" s="93"/>
-      <c r="B98" s="94"/>
-      <c r="C98" s="94"/>
-      <c r="D98" s="94"/>
-      <c r="E98" s="94"/>
-      <c r="F98" s="94"/>
-      <c r="G98" s="94"/>
-      <c r="H98" s="95"/>
+      <c r="A98" s="76"/>
+      <c r="B98" s="77"/>
+      <c r="C98" s="77"/>
+      <c r="D98" s="77"/>
+      <c r="E98" s="77"/>
+      <c r="F98" s="77"/>
+      <c r="G98" s="77"/>
+      <c r="H98" s="78"/>
     </row>
     <row r="99" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A99" s="93"/>
-      <c r="B99" s="94"/>
-      <c r="C99" s="94"/>
-      <c r="D99" s="94"/>
-      <c r="E99" s="94"/>
-      <c r="F99" s="94"/>
-      <c r="G99" s="94"/>
-      <c r="H99" s="95"/>
+      <c r="A99" s="76"/>
+      <c r="B99" s="77"/>
+      <c r="C99" s="77"/>
+      <c r="D99" s="77"/>
+      <c r="E99" s="77"/>
+      <c r="F99" s="77"/>
+      <c r="G99" s="77"/>
+      <c r="H99" s="78"/>
     </row>
     <row r="100" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A100" s="93"/>
-      <c r="B100" s="94"/>
-      <c r="C100" s="94"/>
-      <c r="D100" s="94"/>
-      <c r="E100" s="94"/>
-      <c r="F100" s="94"/>
-      <c r="G100" s="94"/>
-      <c r="H100" s="95"/>
+      <c r="A100" s="76"/>
+      <c r="B100" s="77"/>
+      <c r="C100" s="77"/>
+      <c r="D100" s="77"/>
+      <c r="E100" s="77"/>
+      <c r="F100" s="77"/>
+      <c r="G100" s="77"/>
+      <c r="H100" s="78"/>
     </row>
     <row r="101" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A101" s="93"/>
-      <c r="B101" s="94"/>
-      <c r="C101" s="94"/>
-      <c r="D101" s="94"/>
-      <c r="E101" s="94"/>
-      <c r="F101" s="94"/>
-      <c r="G101" s="94"/>
-      <c r="H101" s="95"/>
+      <c r="A101" s="76"/>
+      <c r="B101" s="77"/>
+      <c r="C101" s="77"/>
+      <c r="D101" s="77"/>
+      <c r="E101" s="77"/>
+      <c r="F101" s="77"/>
+      <c r="G101" s="77"/>
+      <c r="H101" s="78"/>
     </row>
     <row r="102" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A102" s="93"/>
-      <c r="B102" s="94"/>
-      <c r="C102" s="94"/>
-      <c r="D102" s="94"/>
-      <c r="E102" s="94"/>
-      <c r="F102" s="94"/>
-      <c r="G102" s="94"/>
-      <c r="H102" s="95"/>
+      <c r="A102" s="76"/>
+      <c r="B102" s="77"/>
+      <c r="C102" s="77"/>
+      <c r="D102" s="77"/>
+      <c r="E102" s="77"/>
+      <c r="F102" s="77"/>
+      <c r="G102" s="77"/>
+      <c r="H102" s="78"/>
     </row>
     <row r="103" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A103" s="93"/>
-      <c r="B103" s="94"/>
-      <c r="C103" s="94"/>
-      <c r="D103" s="94"/>
-      <c r="E103" s="94"/>
-      <c r="F103" s="94"/>
-      <c r="G103" s="94"/>
-      <c r="H103" s="95"/>
+      <c r="A103" s="76"/>
+      <c r="B103" s="77"/>
+      <c r="C103" s="77"/>
+      <c r="D103" s="77"/>
+      <c r="E103" s="77"/>
+      <c r="F103" s="77"/>
+      <c r="G103" s="77"/>
+      <c r="H103" s="78"/>
     </row>
     <row r="104" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A104" s="93"/>
-      <c r="B104" s="94"/>
-      <c r="C104" s="94"/>
-      <c r="D104" s="94"/>
-      <c r="E104" s="94"/>
-      <c r="F104" s="94"/>
-      <c r="G104" s="94"/>
-      <c r="H104" s="95"/>
+      <c r="A104" s="76"/>
+      <c r="B104" s="77"/>
+      <c r="C104" s="77"/>
+      <c r="D104" s="77"/>
+      <c r="E104" s="77"/>
+      <c r="F104" s="77"/>
+      <c r="G104" s="77"/>
+      <c r="H104" s="78"/>
     </row>
     <row r="105" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A105" s="93"/>
-      <c r="B105" s="94"/>
-      <c r="C105" s="94"/>
-      <c r="D105" s="94"/>
-      <c r="E105" s="94"/>
-      <c r="F105" s="94"/>
-      <c r="G105" s="94"/>
-      <c r="H105" s="95"/>
+      <c r="A105" s="76"/>
+      <c r="B105" s="77"/>
+      <c r="C105" s="77"/>
+      <c r="D105" s="77"/>
+      <c r="E105" s="77"/>
+      <c r="F105" s="77"/>
+      <c r="G105" s="77"/>
+      <c r="H105" s="78"/>
     </row>
     <row r="106" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A106" s="93"/>
-      <c r="B106" s="94"/>
-      <c r="C106" s="94"/>
-      <c r="D106" s="94"/>
-      <c r="E106" s="94"/>
-      <c r="F106" s="94"/>
-      <c r="G106" s="94"/>
-      <c r="H106" s="95"/>
+      <c r="A106" s="76"/>
+      <c r="B106" s="77"/>
+      <c r="C106" s="77"/>
+      <c r="D106" s="77"/>
+      <c r="E106" s="77"/>
+      <c r="F106" s="77"/>
+      <c r="G106" s="77"/>
+      <c r="H106" s="78"/>
     </row>
     <row r="107" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A107" s="96"/>
-      <c r="B107" s="97"/>
-      <c r="C107" s="97"/>
-      <c r="D107" s="97"/>
-      <c r="E107" s="97"/>
-      <c r="F107" s="97"/>
-      <c r="G107" s="97"/>
-      <c r="H107" s="98"/>
+      <c r="A107" s="79"/>
+      <c r="B107" s="80"/>
+      <c r="C107" s="80"/>
+      <c r="D107" s="80"/>
+      <c r="E107" s="80"/>
+      <c r="F107" s="80"/>
+      <c r="G107" s="80"/>
+      <c r="H107" s="81"/>
     </row>
     <row r="108" spans="1:8" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A108" s="99"/>
-      <c r="B108" s="100"/>
-      <c r="C108" s="100"/>
-      <c r="D108" s="100"/>
-      <c r="E108" s="100"/>
-      <c r="F108" s="100"/>
-      <c r="G108" s="100"/>
-      <c r="H108" s="101"/>
+      <c r="A108" s="82"/>
+      <c r="B108" s="83"/>
+      <c r="C108" s="83"/>
+      <c r="D108" s="83"/>
+      <c r="E108" s="83"/>
+      <c r="F108" s="83"/>
+      <c r="G108" s="83"/>
+      <c r="H108" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="A58:D58"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="A11:A12"/>
@@ -3340,11 +3345,16 @@
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="E11:E12"/>
     <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="H11:H12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77D3A35-40BC-47F8-82DD-081E887FE95D}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4B3ABD-127B-44BE-BBF2-5F414A249ED5}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -205,7 +205,7 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -213,7 +213,7 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -835,6 +835,46 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -843,46 +883,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1412,9 +1412,9 @@
   <sheetData>
     <row r="1" spans="1:26" ht="24.6" customHeight="1">
       <c r="A1" s="12"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
       <c r="E1" s="55"/>
       <c r="F1" s="55"/>
       <c r="G1" s="55"/>
@@ -1425,19 +1425,19 @@
       <c r="A2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
       <c r="E2" s="47"/>
       <c r="F2" s="47"/>
       <c r="G2" s="47"/>
       <c r="H2" s="14"/>
     </row>
     <row r="3" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A3" s="88"/>
-      <c r="B3" s="101"/>
-      <c r="C3" s="101"/>
-      <c r="D3" s="101"/>
+      <c r="A3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
       <c r="E3" s="47"/>
       <c r="F3" s="48"/>
       <c r="G3" s="48"/>
@@ -1466,10 +1466,10 @@
       <c r="H5" s="14"/>
     </row>
     <row r="6" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A6" s="88"/>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
+      <c r="A6" s="92"/>
+      <c r="B6" s="94"/>
+      <c r="C6" s="94"/>
+      <c r="D6" s="94"/>
       <c r="E6" s="49"/>
       <c r="F6" s="47"/>
       <c r="G6" s="48"/>
@@ -1480,10 +1480,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="59"/>
-      <c r="C7" s="99" t="s">
+      <c r="C7" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="99"/>
+      <c r="D7" s="90"/>
       <c r="E7" s="59"/>
       <c r="F7" s="60" t="s">
         <v>3</v>
@@ -1494,14 +1494,14 @@
     <row r="8" spans="1:26" ht="33.6" customHeight="1">
       <c r="A8" s="36"/>
       <c r="B8" s="59"/>
-      <c r="C8" s="100"/>
-      <c r="D8" s="100"/>
+      <c r="C8" s="91"/>
+      <c r="D8" s="91"/>
       <c r="E8" s="59"/>
-      <c r="F8" s="98" t="e">
+      <c r="F8" s="87" t="e">
         <f>A8/C8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G8" s="98"/>
+      <c r="G8" s="87"/>
       <c r="H8" s="14"/>
     </row>
     <row r="9" spans="1:26" ht="24.6" customHeight="1">
@@ -1528,28 +1528,28 @@
       <c r="H10" s="14"/>
     </row>
     <row r="11" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A11" s="94" t="s">
+      <c r="A11" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="94" t="s">
+      <c r="B11" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="94" t="s">
+      <c r="C11" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="94" t="s">
+      <c r="D11" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="94" t="s">
+      <c r="E11" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="94" t="s">
+      <c r="F11" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="94" t="s">
+      <c r="G11" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="94" t="s">
+      <c r="H11" s="88" t="s">
         <v>13</v>
       </c>
       <c r="I11" s="3"/>
@@ -1572,14 +1572,14 @@
       <c r="Z11" s="3"/>
     </row>
     <row r="12" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A12" s="95"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
+      <c r="A12" s="89"/>
+      <c r="B12" s="89"/>
+      <c r="C12" s="89"/>
+      <c r="D12" s="89"/>
+      <c r="E12" s="89"/>
+      <c r="F12" s="89"/>
+      <c r="G12" s="89"/>
+      <c r="H12" s="89"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -1613,7 +1613,7 @@
         <f>F13*B13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H13" s="85"/>
+      <c r="H13" s="99"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -1647,7 +1647,7 @@
         <f t="shared" ref="G14:G40" si="1">F14*B14</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H14" s="86"/>
+      <c r="H14" s="100"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -1681,7 +1681,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H15" s="86"/>
+      <c r="H15" s="100"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -1715,7 +1715,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H16" s="86"/>
+      <c r="H16" s="100"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -1749,7 +1749,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H17" s="86"/>
+      <c r="H17" s="100"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
@@ -1783,7 +1783,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H18" s="86"/>
+      <c r="H18" s="100"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
@@ -1817,7 +1817,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H19" s="86"/>
+      <c r="H19" s="100"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -1851,7 +1851,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H20" s="86"/>
+      <c r="H20" s="100"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
@@ -1885,7 +1885,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H21" s="86"/>
+      <c r="H21" s="100"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
@@ -1919,7 +1919,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H22" s="86"/>
+      <c r="H22" s="100"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
@@ -1953,7 +1953,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H23" s="86"/>
+      <c r="H23" s="100"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
@@ -1987,7 +1987,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H24" s="87"/>
+      <c r="H24" s="101"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
@@ -2021,7 +2021,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H25" s="87"/>
+      <c r="H25" s="101"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
@@ -2055,7 +2055,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H26" s="87"/>
+      <c r="H26" s="101"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
@@ -2089,7 +2089,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H27" s="87"/>
+      <c r="H27" s="101"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
@@ -2123,7 +2123,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H28" s="86"/>
+      <c r="H28" s="100"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
@@ -2157,7 +2157,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H29" s="87"/>
+      <c r="H29" s="101"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
@@ -2191,7 +2191,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H30" s="87"/>
+      <c r="H30" s="101"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
@@ -2225,7 +2225,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H31" s="87"/>
+      <c r="H31" s="101"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
@@ -2259,7 +2259,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H32" s="87"/>
+      <c r="H32" s="101"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
@@ -2293,7 +2293,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H33" s="87"/>
+      <c r="H33" s="101"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
@@ -2327,7 +2327,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H34" s="87"/>
+      <c r="H34" s="101"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
@@ -2361,7 +2361,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H35" s="87"/>
+      <c r="H35" s="101"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
@@ -2395,7 +2395,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H36" s="87"/>
+      <c r="H36" s="101"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
@@ -2429,7 +2429,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H37" s="87"/>
+      <c r="H37" s="101"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
@@ -2463,7 +2463,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H38" s="87"/>
+      <c r="H38" s="101"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
@@ -2497,7 +2497,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H39" s="87"/>
+      <c r="H39" s="101"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
@@ -2531,7 +2531,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H40" s="87"/>
+      <c r="H40" s="101"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
@@ -2792,10 +2792,10 @@
       <c r="H54" s="24"/>
     </row>
     <row r="55" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A55" s="88"/>
-      <c r="B55" s="89"/>
-      <c r="C55" s="89"/>
-      <c r="D55" s="89"/>
+      <c r="A55" s="92"/>
+      <c r="B55" s="94"/>
+      <c r="C55" s="94"/>
+      <c r="D55" s="94"/>
       <c r="E55" s="47"/>
       <c r="F55" s="48"/>
       <c r="G55" s="48"/>
@@ -2824,10 +2824,10 @@
       <c r="H57" s="14"/>
     </row>
     <row r="58" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A58" s="88"/>
-      <c r="B58" s="89"/>
-      <c r="C58" s="89"/>
-      <c r="D58" s="89"/>
+      <c r="A58" s="92"/>
+      <c r="B58" s="94"/>
+      <c r="C58" s="94"/>
+      <c r="D58" s="94"/>
       <c r="E58" s="49"/>
       <c r="F58" s="47"/>
       <c r="G58" s="48"/>
@@ -2836,24 +2836,24 @@
     <row r="59" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
       <c r="A59" s="50"/>
       <c r="B59" s="51"/>
-      <c r="C59" s="93"/>
-      <c r="D59" s="93"/>
+      <c r="C59" s="98"/>
+      <c r="D59" s="98"/>
       <c r="E59" s="51"/>
       <c r="F59" s="52"/>
       <c r="G59" s="52"/>
       <c r="H59" s="53"/>
     </row>
     <row r="60" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A60" s="90" t="s">
+      <c r="A60" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="B60" s="91"/>
-      <c r="C60" s="91"/>
-      <c r="D60" s="91"/>
-      <c r="E60" s="91"/>
-      <c r="F60" s="91"/>
-      <c r="G60" s="91"/>
-      <c r="H60" s="92"/>
+      <c r="B60" s="96"/>
+      <c r="C60" s="96"/>
+      <c r="D60" s="96"/>
+      <c r="E60" s="96"/>
+      <c r="F60" s="96"/>
+      <c r="G60" s="96"/>
+      <c r="H60" s="97"/>
     </row>
     <row r="61" spans="1:10" ht="24.6" customHeight="1">
       <c r="A61" s="76"/>
@@ -3337,6 +3337,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="H11:H12"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="A11:A12"/>
@@ -3350,11 +3355,6 @@
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="H11:H12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4B3ABD-127B-44BE-BBF2-5F414A249ED5}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CA3EC4-41C9-4B6F-8DA9-4B1E078983E4}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -685,7 +685,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -766,13 +766,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -835,6 +829,37 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -844,45 +869,14 @@
     <xf numFmtId="1" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1412,12 +1406,12 @@
   <sheetData>
     <row r="1" spans="1:26" ht="24.6" customHeight="1">
       <c r="A1" s="12"/>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
       <c r="H1" s="13"/>
       <c r="I1" s="2"/>
     </row>
@@ -1425,93 +1419,93 @@
       <c r="A2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
       <c r="H2" s="14"/>
     </row>
     <row r="3" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A3" s="92"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
+      <c r="A3" s="86"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
       <c r="H3" s="14"/>
     </row>
     <row r="4" spans="1:26" ht="24.6" customHeight="1">
       <c r="A4" s="15"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
       <c r="H4" s="14"/>
     </row>
     <row r="5" spans="1:26" ht="24.6" customHeight="1">
       <c r="A5" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="48"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="46"/>
       <c r="H5" s="14"/>
     </row>
     <row r="6" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A6" s="92"/>
-      <c r="B6" s="94"/>
-      <c r="C6" s="94"/>
-      <c r="D6" s="94"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="48"/>
+      <c r="A6" s="86"/>
+      <c r="B6" s="87"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="87"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="46"/>
       <c r="H6" s="16"/>
     </row>
     <row r="7" spans="1:26" ht="35.450000000000003" customHeight="1">
       <c r="A7" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="90" t="s">
+      <c r="B7" s="57"/>
+      <c r="C7" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="90"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="60" t="s">
+      <c r="D7" s="97"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="60"/>
+      <c r="G7" s="58"/>
       <c r="H7" s="16"/>
     </row>
     <row r="8" spans="1:26" ht="33.6" customHeight="1">
       <c r="A8" s="36"/>
-      <c r="B8" s="59"/>
-      <c r="C8" s="91"/>
-      <c r="D8" s="91"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="87" t="e">
+      <c r="B8" s="57"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="96" t="e">
         <f>A8/C8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G8" s="87"/>
+      <c r="G8" s="96"/>
       <c r="H8" s="14"/>
     </row>
     <row r="9" spans="1:26" ht="24.6" customHeight="1">
       <c r="A9" s="15"/>
-      <c r="B9" s="61"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
       <c r="H9" s="17"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -1519,37 +1513,37 @@
     </row>
     <row r="10" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
       <c r="A10" s="15"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
       <c r="H10" s="14"/>
     </row>
     <row r="11" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A11" s="88" t="s">
+      <c r="A11" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="88" t="s">
+      <c r="B11" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="88" t="s">
+      <c r="C11" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="88" t="s">
+      <c r="D11" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="88" t="s">
+      <c r="E11" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="88" t="s">
+      <c r="F11" s="92" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="88" t="s">
+      <c r="G11" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="88" t="s">
+      <c r="H11" s="92" t="s">
         <v>13</v>
       </c>
       <c r="I11" s="3"/>
@@ -1572,14 +1566,14 @@
       <c r="Z11" s="3"/>
     </row>
     <row r="12" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A12" s="89"/>
-      <c r="B12" s="89"/>
-      <c r="C12" s="89"/>
-      <c r="D12" s="89"/>
-      <c r="E12" s="89"/>
-      <c r="F12" s="89"/>
-      <c r="G12" s="89"/>
-      <c r="H12" s="89"/>
+      <c r="A12" s="93"/>
+      <c r="B12" s="93"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -1613,7 +1607,7 @@
         <f>F13*B13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H13" s="99"/>
+      <c r="H13" s="83"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -1647,7 +1641,7 @@
         <f t="shared" ref="G14:G40" si="1">F14*B14</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H14" s="100"/>
+      <c r="H14" s="84"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -1681,7 +1675,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H15" s="100"/>
+      <c r="H15" s="84"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -1715,7 +1709,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H16" s="100"/>
+      <c r="H16" s="84"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -1749,7 +1743,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H17" s="100"/>
+      <c r="H17" s="84"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
@@ -1783,7 +1777,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H18" s="100"/>
+      <c r="H18" s="84"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
@@ -1817,7 +1811,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H19" s="100"/>
+      <c r="H19" s="84"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -1851,7 +1845,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H20" s="100"/>
+      <c r="H20" s="84"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
@@ -1885,7 +1879,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H21" s="100"/>
+      <c r="H21" s="84"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
@@ -1919,7 +1913,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H22" s="100"/>
+      <c r="H22" s="84"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
@@ -1953,7 +1947,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H23" s="100"/>
+      <c r="H23" s="84"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
@@ -1987,7 +1981,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H24" s="101"/>
+      <c r="H24" s="85"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
@@ -2021,7 +2015,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H25" s="101"/>
+      <c r="H25" s="85"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
@@ -2055,7 +2049,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H26" s="101"/>
+      <c r="H26" s="85"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
@@ -2089,7 +2083,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H27" s="101"/>
+      <c r="H27" s="85"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
@@ -2123,7 +2117,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H28" s="100"/>
+      <c r="H28" s="84"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
@@ -2157,7 +2151,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H29" s="101"/>
+      <c r="H29" s="85"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
@@ -2191,7 +2185,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H30" s="101"/>
+      <c r="H30" s="85"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
@@ -2225,7 +2219,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H31" s="101"/>
+      <c r="H31" s="85"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
@@ -2259,7 +2253,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H32" s="101"/>
+      <c r="H32" s="85"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
@@ -2293,7 +2287,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H33" s="101"/>
+      <c r="H33" s="85"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
@@ -2327,7 +2321,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H34" s="101"/>
+      <c r="H34" s="85"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
@@ -2361,7 +2355,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H35" s="101"/>
+      <c r="H35" s="85"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
@@ -2395,7 +2389,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H36" s="101"/>
+      <c r="H36" s="85"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
@@ -2429,7 +2423,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H37" s="101"/>
+      <c r="H37" s="85"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
@@ -2463,7 +2457,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H38" s="101"/>
+      <c r="H38" s="85"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
@@ -2497,7 +2491,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H39" s="101"/>
+      <c r="H39" s="85"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
@@ -2531,7 +2525,7 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H40" s="101"/>
+      <c r="H40" s="85"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
@@ -2637,11 +2631,11 @@
     </row>
     <row r="44" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
       <c r="A44" s="15"/>
-      <c r="B44" s="47"/>
-      <c r="C44" s="47"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="47"/>
+      <c r="B44" s="45"/>
+      <c r="C44" s="45"/>
+      <c r="D44" s="45"/>
+      <c r="E44" s="45"/>
+      <c r="F44" s="45"/>
       <c r="G44" s="7"/>
       <c r="H44" s="19"/>
     </row>
@@ -2653,25 +2647,25 @@
       <c r="C45" s="23"/>
       <c r="D45" s="23"/>
       <c r="E45" s="24"/>
-      <c r="F45" s="67" t="s">
+      <c r="F45" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="G45" s="68" t="e">
+      <c r="G45" s="66" t="e">
         <f>SUM(G13:G43)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H45" s="69" t="s">
+      <c r="H45" s="67" t="s">
         <v>16</v>
       </c>
       <c r="K45" s="10"/>
     </row>
     <row r="46" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A46" s="42"/>
-      <c r="B46" s="62"/>
-      <c r="C46" s="62"/>
-      <c r="D46" s="62"/>
-      <c r="E46" s="43"/>
-      <c r="F46" s="70" t="s">
+      <c r="A46" s="74"/>
+      <c r="B46" s="60"/>
+      <c r="C46" s="60"/>
+      <c r="D46" s="60"/>
+      <c r="E46" s="42"/>
+      <c r="F46" s="68" t="s">
         <v>8</v>
       </c>
       <c r="G46" s="9"/>
@@ -2679,41 +2673,41 @@
       <c r="K46" s="10"/>
     </row>
     <row r="47" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A47" s="42"/>
-      <c r="B47" s="62"/>
-      <c r="C47" s="62"/>
-      <c r="D47" s="62"/>
-      <c r="E47" s="43"/>
-      <c r="F47" s="70" t="s">
+      <c r="A47" s="74"/>
+      <c r="B47" s="60"/>
+      <c r="C47" s="60"/>
+      <c r="D47" s="60"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="68" t="s">
         <v>10</v>
       </c>
       <c r="G47" s="25" t="e">
         <f>SUM(G45,G46)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H47" s="73"/>
+      <c r="H47" s="71"/>
       <c r="K47" s="11"/>
     </row>
     <row r="48" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A48" s="42"/>
-      <c r="B48" s="62"/>
-      <c r="C48" s="62"/>
-      <c r="D48" s="62"/>
-      <c r="E48" s="43"/>
-      <c r="F48" s="71" t="s">
+      <c r="A48" s="74"/>
+      <c r="B48" s="60"/>
+      <c r="C48" s="60"/>
+      <c r="D48" s="60"/>
+      <c r="E48" s="42"/>
+      <c r="F48" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="G48" s="54"/>
+      <c r="G48" s="52"/>
       <c r="H48" s="14"/>
       <c r="K48" s="10"/>
     </row>
     <row r="49" spans="1:10" ht="24.6" customHeight="1">
-      <c r="A49" s="42"/>
-      <c r="B49" s="62"/>
-      <c r="C49" s="62"/>
-      <c r="D49" s="62"/>
-      <c r="E49" s="43"/>
-      <c r="F49" s="70" t="s">
+      <c r="A49" s="74"/>
+      <c r="B49" s="60"/>
+      <c r="C49" s="60"/>
+      <c r="D49" s="60"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="68" t="s">
         <v>12</v>
       </c>
       <c r="G49" s="26" t="e">
@@ -2726,40 +2720,40 @@
       <c r="J49" s="8"/>
     </row>
     <row r="50" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A50" s="42"/>
-      <c r="B50" s="62"/>
-      <c r="C50" s="62"/>
-      <c r="D50" s="62"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="72"/>
+      <c r="A50" s="74"/>
+      <c r="B50" s="60"/>
+      <c r="C50" s="60"/>
+      <c r="D50" s="60"/>
+      <c r="E50" s="42"/>
+      <c r="F50" s="70"/>
       <c r="G50" s="27"/>
       <c r="H50" s="29"/>
       <c r="I50" s="8"/>
       <c r="J50" s="8"/>
     </row>
     <row r="51" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A51" s="42"/>
-      <c r="B51" s="62"/>
-      <c r="C51" s="62"/>
-      <c r="D51" s="62"/>
-      <c r="E51" s="43"/>
-      <c r="F51" s="71" t="s">
+      <c r="A51" s="74"/>
+      <c r="B51" s="60"/>
+      <c r="C51" s="60"/>
+      <c r="D51" s="60"/>
+      <c r="E51" s="42"/>
+      <c r="F51" s="69" t="s">
         <v>15</v>
       </c>
       <c r="G51" s="28" t="e">
         <f>G47/F8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H51" s="73"/>
+      <c r="H51" s="71"/>
       <c r="I51" s="8"/>
       <c r="J51" s="8"/>
     </row>
     <row r="52" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A52" s="44"/>
-      <c r="B52" s="45"/>
-      <c r="C52" s="45"/>
-      <c r="D52" s="45"/>
-      <c r="E52" s="46"/>
+      <c r="A52" s="74"/>
+      <c r="B52" s="43"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="44"/>
       <c r="F52" s="37" t="s">
         <v>14</v>
       </c>
@@ -2770,578 +2764,573 @@
       <c r="H52" s="21"/>
     </row>
     <row r="53" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A53" s="63"/>
-      <c r="B53" s="64"/>
-      <c r="C53" s="64"/>
-      <c r="D53" s="64"/>
-      <c r="E53" s="65"/>
-      <c r="F53" s="65"/>
-      <c r="G53" s="65"/>
-      <c r="H53" s="66"/>
+      <c r="A53" s="61"/>
+      <c r="B53" s="62"/>
+      <c r="C53" s="62"/>
+      <c r="D53" s="62"/>
+      <c r="E53" s="63"/>
+      <c r="F53" s="63"/>
+      <c r="G53" s="63"/>
+      <c r="H53" s="64"/>
     </row>
     <row r="54" spans="1:10" ht="24.6" customHeight="1">
-      <c r="A54" s="58" t="s">
+      <c r="A54" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B54" s="57"/>
-      <c r="C54" s="57"/>
-      <c r="D54" s="57"/>
+      <c r="B54" s="55"/>
+      <c r="C54" s="55"/>
+      <c r="D54" s="55"/>
       <c r="E54" s="23"/>
       <c r="F54" s="23"/>
       <c r="G54" s="23"/>
       <c r="H54" s="24"/>
     </row>
     <row r="55" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A55" s="92"/>
-      <c r="B55" s="94"/>
-      <c r="C55" s="94"/>
-      <c r="D55" s="94"/>
-      <c r="E55" s="47"/>
-      <c r="F55" s="48"/>
-      <c r="G55" s="48"/>
+      <c r="A55" s="86"/>
+      <c r="B55" s="87"/>
+      <c r="C55" s="87"/>
+      <c r="D55" s="87"/>
+      <c r="E55" s="45"/>
+      <c r="F55" s="46"/>
+      <c r="G55" s="46"/>
       <c r="H55" s="14"/>
     </row>
     <row r="56" spans="1:10" ht="24.6" customHeight="1">
       <c r="A56" s="15"/>
-      <c r="B56" s="47"/>
-      <c r="C56" s="47"/>
-      <c r="D56" s="47"/>
-      <c r="E56" s="47"/>
-      <c r="F56" s="48"/>
-      <c r="G56" s="48"/>
+      <c r="B56" s="45"/>
+      <c r="C56" s="45"/>
+      <c r="D56" s="45"/>
+      <c r="E56" s="45"/>
+      <c r="F56" s="46"/>
+      <c r="G56" s="46"/>
       <c r="H56" s="14"/>
     </row>
     <row r="57" spans="1:10" ht="24.6" customHeight="1">
       <c r="A57" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B57" s="47"/>
-      <c r="C57" s="47"/>
-      <c r="D57" s="47"/>
-      <c r="E57" s="47"/>
-      <c r="F57" s="47"/>
-      <c r="G57" s="48"/>
+      <c r="B57" s="45"/>
+      <c r="C57" s="45"/>
+      <c r="D57" s="45"/>
+      <c r="E57" s="45"/>
+      <c r="F57" s="45"/>
+      <c r="G57" s="46"/>
       <c r="H57" s="14"/>
     </row>
     <row r="58" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A58" s="92"/>
-      <c r="B58" s="94"/>
-      <c r="C58" s="94"/>
-      <c r="D58" s="94"/>
-      <c r="E58" s="49"/>
-      <c r="F58" s="47"/>
-      <c r="G58" s="48"/>
+      <c r="A58" s="86"/>
+      <c r="B58" s="87"/>
+      <c r="C58" s="87"/>
+      <c r="D58" s="87"/>
+      <c r="E58" s="47"/>
+      <c r="F58" s="45"/>
+      <c r="G58" s="46"/>
       <c r="H58" s="16"/>
     </row>
     <row r="59" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A59" s="50"/>
-      <c r="B59" s="51"/>
-      <c r="C59" s="98"/>
-      <c r="D59" s="98"/>
-      <c r="E59" s="51"/>
-      <c r="F59" s="52"/>
-      <c r="G59" s="52"/>
-      <c r="H59" s="53"/>
+      <c r="A59" s="48"/>
+      <c r="B59" s="49"/>
+      <c r="C59" s="91"/>
+      <c r="D59" s="91"/>
+      <c r="E59" s="49"/>
+      <c r="F59" s="50"/>
+      <c r="G59" s="50"/>
+      <c r="H59" s="51"/>
     </row>
     <row r="60" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A60" s="95" t="s">
+      <c r="A60" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="B60" s="96"/>
-      <c r="C60" s="96"/>
-      <c r="D60" s="96"/>
-      <c r="E60" s="96"/>
-      <c r="F60" s="96"/>
-      <c r="G60" s="96"/>
-      <c r="H60" s="97"/>
+      <c r="B60" s="89"/>
+      <c r="C60" s="89"/>
+      <c r="D60" s="89"/>
+      <c r="E60" s="89"/>
+      <c r="F60" s="89"/>
+      <c r="G60" s="89"/>
+      <c r="H60" s="90"/>
     </row>
     <row r="61" spans="1:10" ht="24.6" customHeight="1">
-      <c r="A61" s="76"/>
-      <c r="B61" s="74"/>
-      <c r="C61" s="74"/>
-      <c r="D61" s="74"/>
-      <c r="E61" s="74"/>
-      <c r="F61" s="74"/>
-      <c r="G61" s="74"/>
-      <c r="H61" s="75"/>
+      <c r="A61" s="74"/>
+      <c r="B61" s="72"/>
+      <c r="C61" s="72"/>
+      <c r="D61" s="72"/>
+      <c r="E61" s="72"/>
+      <c r="F61" s="72"/>
+      <c r="G61" s="72"/>
+      <c r="H61" s="73"/>
     </row>
     <row r="62" spans="1:10" ht="24.6" customHeight="1">
-      <c r="A62" s="76"/>
-      <c r="B62" s="74"/>
-      <c r="C62" s="74"/>
-      <c r="D62" s="74"/>
-      <c r="E62" s="74"/>
-      <c r="F62" s="74"/>
-      <c r="G62" s="74"/>
-      <c r="H62" s="75"/>
+      <c r="A62" s="74"/>
+      <c r="B62" s="72"/>
+      <c r="C62" s="72"/>
+      <c r="D62" s="72"/>
+      <c r="E62" s="72"/>
+      <c r="F62" s="72"/>
+      <c r="G62" s="72"/>
+      <c r="H62" s="73"/>
     </row>
     <row r="63" spans="1:10" ht="24.6" customHeight="1">
-      <c r="A63" s="76"/>
-      <c r="B63" s="74"/>
-      <c r="C63" s="74"/>
-      <c r="D63" s="74"/>
-      <c r="E63" s="74"/>
-      <c r="F63" s="74"/>
-      <c r="G63" s="74"/>
-      <c r="H63" s="75"/>
+      <c r="A63" s="74"/>
+      <c r="B63" s="72"/>
+      <c r="C63" s="72"/>
+      <c r="D63" s="72"/>
+      <c r="E63" s="72"/>
+      <c r="F63" s="72"/>
+      <c r="G63" s="72"/>
+      <c r="H63" s="73"/>
     </row>
     <row r="64" spans="1:10" ht="24.6" customHeight="1">
-      <c r="A64" s="76"/>
-      <c r="B64" s="77"/>
-      <c r="C64" s="77"/>
-      <c r="D64" s="77"/>
-      <c r="E64" s="77"/>
-      <c r="F64" s="77"/>
-      <c r="G64" s="77"/>
-      <c r="H64" s="78"/>
+      <c r="A64" s="74"/>
+      <c r="B64" s="75"/>
+      <c r="C64" s="75"/>
+      <c r="D64" s="75"/>
+      <c r="E64" s="75"/>
+      <c r="F64" s="75"/>
+      <c r="G64" s="75"/>
+      <c r="H64" s="76"/>
     </row>
     <row r="65" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A65" s="76"/>
-      <c r="B65" s="77"/>
-      <c r="C65" s="77"/>
-      <c r="D65" s="77"/>
-      <c r="E65" s="77"/>
-      <c r="F65" s="77"/>
-      <c r="G65" s="77"/>
-      <c r="H65" s="78"/>
+      <c r="A65" s="74"/>
+      <c r="B65" s="75"/>
+      <c r="C65" s="75"/>
+      <c r="D65" s="75"/>
+      <c r="E65" s="75"/>
+      <c r="F65" s="75"/>
+      <c r="G65" s="75"/>
+      <c r="H65" s="76"/>
     </row>
     <row r="66" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A66" s="76"/>
-      <c r="B66" s="77"/>
-      <c r="C66" s="77"/>
-      <c r="D66" s="77"/>
-      <c r="E66" s="77"/>
-      <c r="F66" s="77"/>
-      <c r="G66" s="77"/>
-      <c r="H66" s="78"/>
+      <c r="A66" s="74"/>
+      <c r="B66" s="75"/>
+      <c r="C66" s="75"/>
+      <c r="D66" s="75"/>
+      <c r="E66" s="75"/>
+      <c r="F66" s="75"/>
+      <c r="G66" s="75"/>
+      <c r="H66" s="76"/>
     </row>
     <row r="67" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A67" s="76"/>
-      <c r="B67" s="77"/>
-      <c r="C67" s="77"/>
-      <c r="D67" s="77"/>
-      <c r="E67" s="77"/>
-      <c r="F67" s="77"/>
-      <c r="G67" s="77"/>
-      <c r="H67" s="78"/>
+      <c r="A67" s="74"/>
+      <c r="B67" s="75"/>
+      <c r="C67" s="75"/>
+      <c r="D67" s="75"/>
+      <c r="E67" s="75"/>
+      <c r="F67" s="75"/>
+      <c r="G67" s="75"/>
+      <c r="H67" s="76"/>
     </row>
     <row r="68" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A68" s="76"/>
-      <c r="B68" s="77"/>
-      <c r="C68" s="77"/>
-      <c r="D68" s="77"/>
-      <c r="E68" s="77"/>
-      <c r="F68" s="77"/>
-      <c r="G68" s="77"/>
-      <c r="H68" s="78"/>
+      <c r="A68" s="74"/>
+      <c r="B68" s="75"/>
+      <c r="C68" s="75"/>
+      <c r="D68" s="75"/>
+      <c r="E68" s="75"/>
+      <c r="F68" s="75"/>
+      <c r="G68" s="75"/>
+      <c r="H68" s="76"/>
     </row>
     <row r="69" spans="1:8" ht="27.6" customHeight="1">
-      <c r="A69" s="76"/>
-      <c r="B69" s="77"/>
-      <c r="C69" s="77"/>
-      <c r="D69" s="77"/>
-      <c r="E69" s="77"/>
-      <c r="F69" s="77"/>
-      <c r="G69" s="77"/>
-      <c r="H69" s="78"/>
+      <c r="A69" s="74"/>
+      <c r="B69" s="75"/>
+      <c r="C69" s="75"/>
+      <c r="D69" s="75"/>
+      <c r="E69" s="75"/>
+      <c r="F69" s="75"/>
+      <c r="G69" s="75"/>
+      <c r="H69" s="76"/>
     </row>
     <row r="70" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A70" s="76"/>
-      <c r="B70" s="77"/>
-      <c r="C70" s="77"/>
-      <c r="D70" s="77"/>
-      <c r="E70" s="77"/>
-      <c r="F70" s="77"/>
-      <c r="G70" s="77"/>
-      <c r="H70" s="78"/>
+      <c r="A70" s="74"/>
+      <c r="B70" s="75"/>
+      <c r="C70" s="75"/>
+      <c r="D70" s="75"/>
+      <c r="E70" s="75"/>
+      <c r="F70" s="75"/>
+      <c r="G70" s="75"/>
+      <c r="H70" s="76"/>
     </row>
     <row r="71" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A71" s="76"/>
-      <c r="B71" s="77"/>
-      <c r="C71" s="77"/>
-      <c r="D71" s="77"/>
-      <c r="E71" s="77"/>
-      <c r="F71" s="77"/>
-      <c r="G71" s="77"/>
-      <c r="H71" s="78"/>
+      <c r="A71" s="74"/>
+      <c r="B71" s="75"/>
+      <c r="C71" s="75"/>
+      <c r="D71" s="75"/>
+      <c r="E71" s="75"/>
+      <c r="F71" s="75"/>
+      <c r="G71" s="75"/>
+      <c r="H71" s="76"/>
     </row>
     <row r="72" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A72" s="76"/>
-      <c r="B72" s="77"/>
-      <c r="C72" s="77"/>
-      <c r="D72" s="77"/>
-      <c r="E72" s="77"/>
-      <c r="F72" s="77"/>
-      <c r="G72" s="77"/>
-      <c r="H72" s="78"/>
+      <c r="A72" s="74"/>
+      <c r="B72" s="75"/>
+      <c r="C72" s="75"/>
+      <c r="D72" s="75"/>
+      <c r="E72" s="75"/>
+      <c r="F72" s="75"/>
+      <c r="G72" s="75"/>
+      <c r="H72" s="76"/>
     </row>
     <row r="73" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A73" s="76"/>
-      <c r="B73" s="77"/>
-      <c r="C73" s="77"/>
-      <c r="D73" s="77"/>
-      <c r="E73" s="77"/>
-      <c r="F73" s="77"/>
-      <c r="G73" s="77"/>
-      <c r="H73" s="78"/>
+      <c r="A73" s="74"/>
+      <c r="B73" s="75"/>
+      <c r="C73" s="75"/>
+      <c r="D73" s="75"/>
+      <c r="E73" s="75"/>
+      <c r="F73" s="75"/>
+      <c r="G73" s="75"/>
+      <c r="H73" s="76"/>
     </row>
     <row r="74" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A74" s="76"/>
-      <c r="B74" s="77"/>
-      <c r="C74" s="77"/>
-      <c r="D74" s="77"/>
-      <c r="E74" s="77"/>
-      <c r="F74" s="77"/>
-      <c r="G74" s="77"/>
-      <c r="H74" s="78"/>
+      <c r="A74" s="74"/>
+      <c r="B74" s="75"/>
+      <c r="C74" s="75"/>
+      <c r="D74" s="75"/>
+      <c r="E74" s="75"/>
+      <c r="F74" s="75"/>
+      <c r="G74" s="75"/>
+      <c r="H74" s="76"/>
     </row>
     <row r="75" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A75" s="76"/>
-      <c r="B75" s="77"/>
-      <c r="C75" s="77"/>
-      <c r="D75" s="77"/>
-      <c r="E75" s="77"/>
-      <c r="F75" s="77"/>
-      <c r="G75" s="77"/>
-      <c r="H75" s="78"/>
+      <c r="A75" s="74"/>
+      <c r="B75" s="75"/>
+      <c r="C75" s="75"/>
+      <c r="D75" s="75"/>
+      <c r="E75" s="75"/>
+      <c r="F75" s="75"/>
+      <c r="G75" s="75"/>
+      <c r="H75" s="76"/>
     </row>
     <row r="76" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A76" s="76"/>
-      <c r="B76" s="77"/>
-      <c r="C76" s="77"/>
-      <c r="D76" s="77"/>
-      <c r="E76" s="77"/>
-      <c r="F76" s="77"/>
-      <c r="G76" s="77"/>
-      <c r="H76" s="78"/>
+      <c r="A76" s="74"/>
+      <c r="B76" s="75"/>
+      <c r="C76" s="75"/>
+      <c r="D76" s="75"/>
+      <c r="E76" s="75"/>
+      <c r="F76" s="75"/>
+      <c r="G76" s="75"/>
+      <c r="H76" s="76"/>
     </row>
     <row r="77" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A77" s="76"/>
-      <c r="B77" s="77"/>
-      <c r="C77" s="77"/>
-      <c r="D77" s="77"/>
-      <c r="E77" s="77"/>
-      <c r="F77" s="77"/>
-      <c r="G77" s="77"/>
-      <c r="H77" s="78"/>
+      <c r="A77" s="74"/>
+      <c r="B77" s="75"/>
+      <c r="C77" s="75"/>
+      <c r="D77" s="75"/>
+      <c r="E77" s="75"/>
+      <c r="F77" s="75"/>
+      <c r="G77" s="75"/>
+      <c r="H77" s="76"/>
     </row>
     <row r="78" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A78" s="76"/>
-      <c r="B78" s="77"/>
-      <c r="C78" s="77"/>
-      <c r="D78" s="77"/>
-      <c r="E78" s="77"/>
-      <c r="F78" s="77"/>
-      <c r="G78" s="77"/>
-      <c r="H78" s="78"/>
+      <c r="A78" s="74"/>
+      <c r="B78" s="75"/>
+      <c r="C78" s="75"/>
+      <c r="D78" s="75"/>
+      <c r="E78" s="75"/>
+      <c r="F78" s="75"/>
+      <c r="G78" s="75"/>
+      <c r="H78" s="76"/>
     </row>
     <row r="79" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A79" s="76"/>
-      <c r="B79" s="77"/>
-      <c r="C79" s="77"/>
-      <c r="D79" s="77"/>
-      <c r="E79" s="77"/>
-      <c r="F79" s="77"/>
-      <c r="G79" s="77"/>
-      <c r="H79" s="78"/>
+      <c r="A79" s="74"/>
+      <c r="B79" s="75"/>
+      <c r="C79" s="75"/>
+      <c r="D79" s="75"/>
+      <c r="E79" s="75"/>
+      <c r="F79" s="75"/>
+      <c r="G79" s="75"/>
+      <c r="H79" s="76"/>
     </row>
     <row r="80" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A80" s="76"/>
-      <c r="B80" s="77"/>
-      <c r="C80" s="77"/>
-      <c r="D80" s="77"/>
-      <c r="E80" s="77"/>
-      <c r="F80" s="77"/>
-      <c r="G80" s="77"/>
-      <c r="H80" s="78"/>
+      <c r="A80" s="74"/>
+      <c r="B80" s="75"/>
+      <c r="C80" s="75"/>
+      <c r="D80" s="75"/>
+      <c r="E80" s="75"/>
+      <c r="F80" s="75"/>
+      <c r="G80" s="75"/>
+      <c r="H80" s="76"/>
     </row>
     <row r="81" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A81" s="76"/>
-      <c r="B81" s="77"/>
-      <c r="C81" s="77"/>
-      <c r="D81" s="77"/>
-      <c r="E81" s="77"/>
-      <c r="F81" s="77"/>
-      <c r="G81" s="77"/>
-      <c r="H81" s="78"/>
+      <c r="A81" s="74"/>
+      <c r="B81" s="75"/>
+      <c r="C81" s="75"/>
+      <c r="D81" s="75"/>
+      <c r="E81" s="75"/>
+      <c r="F81" s="75"/>
+      <c r="G81" s="75"/>
+      <c r="H81" s="76"/>
     </row>
     <row r="82" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A82" s="76"/>
-      <c r="B82" s="77"/>
-      <c r="C82" s="77"/>
-      <c r="D82" s="77"/>
-      <c r="E82" s="77"/>
-      <c r="F82" s="77"/>
-      <c r="G82" s="77"/>
-      <c r="H82" s="78"/>
+      <c r="A82" s="74"/>
+      <c r="B82" s="75"/>
+      <c r="C82" s="75"/>
+      <c r="D82" s="75"/>
+      <c r="E82" s="75"/>
+      <c r="F82" s="75"/>
+      <c r="G82" s="75"/>
+      <c r="H82" s="76"/>
     </row>
     <row r="83" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A83" s="76"/>
-      <c r="B83" s="77"/>
-      <c r="C83" s="77"/>
-      <c r="D83" s="77"/>
-      <c r="E83" s="77"/>
-      <c r="F83" s="77"/>
-      <c r="G83" s="77"/>
-      <c r="H83" s="78"/>
+      <c r="A83" s="74"/>
+      <c r="B83" s="75"/>
+      <c r="C83" s="75"/>
+      <c r="D83" s="75"/>
+      <c r="E83" s="75"/>
+      <c r="F83" s="75"/>
+      <c r="G83" s="75"/>
+      <c r="H83" s="76"/>
     </row>
     <row r="84" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A84" s="76"/>
-      <c r="B84" s="77"/>
-      <c r="C84" s="77"/>
-      <c r="D84" s="77"/>
-      <c r="E84" s="77"/>
-      <c r="F84" s="77"/>
-      <c r="G84" s="77"/>
-      <c r="H84" s="78"/>
+      <c r="A84" s="74"/>
+      <c r="B84" s="75"/>
+      <c r="C84" s="75"/>
+      <c r="D84" s="75"/>
+      <c r="E84" s="75"/>
+      <c r="F84" s="75"/>
+      <c r="G84" s="75"/>
+      <c r="H84" s="76"/>
     </row>
     <row r="85" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A85" s="76"/>
-      <c r="B85" s="77"/>
-      <c r="C85" s="77"/>
-      <c r="D85" s="77"/>
-      <c r="E85" s="77"/>
-      <c r="F85" s="77"/>
-      <c r="G85" s="77"/>
-      <c r="H85" s="78"/>
+      <c r="A85" s="74"/>
+      <c r="B85" s="75"/>
+      <c r="C85" s="75"/>
+      <c r="D85" s="75"/>
+      <c r="E85" s="75"/>
+      <c r="F85" s="75"/>
+      <c r="G85" s="75"/>
+      <c r="H85" s="76"/>
     </row>
     <row r="86" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A86" s="76"/>
-      <c r="B86" s="77"/>
-      <c r="C86" s="77"/>
-      <c r="D86" s="77"/>
-      <c r="E86" s="77"/>
-      <c r="F86" s="77"/>
-      <c r="G86" s="77"/>
-      <c r="H86" s="78"/>
+      <c r="A86" s="74"/>
+      <c r="B86" s="75"/>
+      <c r="C86" s="75"/>
+      <c r="D86" s="75"/>
+      <c r="E86" s="75"/>
+      <c r="F86" s="75"/>
+      <c r="G86" s="75"/>
+      <c r="H86" s="76"/>
     </row>
     <row r="87" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A87" s="76"/>
-      <c r="B87" s="77"/>
-      <c r="C87" s="77"/>
-      <c r="D87" s="77"/>
-      <c r="E87" s="77"/>
-      <c r="F87" s="77"/>
-      <c r="G87" s="77"/>
-      <c r="H87" s="78"/>
+      <c r="A87" s="74"/>
+      <c r="B87" s="75"/>
+      <c r="C87" s="75"/>
+      <c r="D87" s="75"/>
+      <c r="E87" s="75"/>
+      <c r="F87" s="75"/>
+      <c r="G87" s="75"/>
+      <c r="H87" s="76"/>
     </row>
     <row r="88" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A88" s="76"/>
-      <c r="B88" s="77"/>
-      <c r="C88" s="77"/>
-      <c r="D88" s="77"/>
-      <c r="E88" s="77"/>
-      <c r="F88" s="77"/>
-      <c r="G88" s="77"/>
-      <c r="H88" s="78"/>
+      <c r="A88" s="74"/>
+      <c r="B88" s="75"/>
+      <c r="C88" s="75"/>
+      <c r="D88" s="75"/>
+      <c r="E88" s="75"/>
+      <c r="F88" s="75"/>
+      <c r="G88" s="75"/>
+      <c r="H88" s="76"/>
     </row>
     <row r="89" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A89" s="76"/>
-      <c r="B89" s="77"/>
-      <c r="C89" s="77"/>
-      <c r="D89" s="77"/>
-      <c r="E89" s="77"/>
-      <c r="F89" s="77"/>
-      <c r="G89" s="77"/>
-      <c r="H89" s="78"/>
+      <c r="A89" s="74"/>
+      <c r="B89" s="75"/>
+      <c r="C89" s="75"/>
+      <c r="D89" s="75"/>
+      <c r="E89" s="75"/>
+      <c r="F89" s="75"/>
+      <c r="G89" s="75"/>
+      <c r="H89" s="76"/>
     </row>
     <row r="90" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A90" s="76"/>
-      <c r="B90" s="77"/>
-      <c r="C90" s="77"/>
-      <c r="D90" s="77"/>
-      <c r="E90" s="77"/>
-      <c r="F90" s="77"/>
-      <c r="G90" s="77"/>
-      <c r="H90" s="78"/>
+      <c r="A90" s="74"/>
+      <c r="B90" s="75"/>
+      <c r="C90" s="75"/>
+      <c r="D90" s="75"/>
+      <c r="E90" s="75"/>
+      <c r="F90" s="75"/>
+      <c r="G90" s="75"/>
+      <c r="H90" s="76"/>
     </row>
     <row r="91" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A91" s="76"/>
-      <c r="B91" s="77"/>
-      <c r="C91" s="77"/>
-      <c r="D91" s="77"/>
-      <c r="E91" s="77"/>
-      <c r="F91" s="77"/>
-      <c r="G91" s="77"/>
-      <c r="H91" s="78"/>
+      <c r="A91" s="74"/>
+      <c r="B91" s="75"/>
+      <c r="C91" s="75"/>
+      <c r="D91" s="75"/>
+      <c r="E91" s="75"/>
+      <c r="F91" s="75"/>
+      <c r="G91" s="75"/>
+      <c r="H91" s="76"/>
     </row>
     <row r="92" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A92" s="76"/>
-      <c r="B92" s="77"/>
-      <c r="C92" s="77"/>
-      <c r="D92" s="77"/>
-      <c r="E92" s="77"/>
-      <c r="F92" s="77"/>
-      <c r="G92" s="77"/>
-      <c r="H92" s="78"/>
+      <c r="A92" s="74"/>
+      <c r="B92" s="75"/>
+      <c r="C92" s="75"/>
+      <c r="D92" s="75"/>
+      <c r="E92" s="75"/>
+      <c r="F92" s="75"/>
+      <c r="G92" s="75"/>
+      <c r="H92" s="76"/>
     </row>
     <row r="93" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A93" s="76"/>
-      <c r="B93" s="77"/>
-      <c r="C93" s="77"/>
-      <c r="D93" s="77"/>
-      <c r="E93" s="77"/>
-      <c r="F93" s="77"/>
-      <c r="G93" s="77"/>
-      <c r="H93" s="78"/>
+      <c r="A93" s="74"/>
+      <c r="B93" s="75"/>
+      <c r="C93" s="75"/>
+      <c r="D93" s="75"/>
+      <c r="E93" s="75"/>
+      <c r="F93" s="75"/>
+      <c r="G93" s="75"/>
+      <c r="H93" s="76"/>
     </row>
     <row r="94" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A94" s="76"/>
-      <c r="B94" s="77"/>
-      <c r="C94" s="77"/>
-      <c r="D94" s="77"/>
-      <c r="E94" s="77"/>
-      <c r="F94" s="77"/>
-      <c r="G94" s="77"/>
-      <c r="H94" s="78"/>
+      <c r="A94" s="74"/>
+      <c r="B94" s="75"/>
+      <c r="C94" s="75"/>
+      <c r="D94" s="75"/>
+      <c r="E94" s="75"/>
+      <c r="F94" s="75"/>
+      <c r="G94" s="75"/>
+      <c r="H94" s="76"/>
     </row>
     <row r="95" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A95" s="76"/>
-      <c r="B95" s="77"/>
-      <c r="C95" s="77"/>
-      <c r="D95" s="77"/>
-      <c r="E95" s="77"/>
-      <c r="F95" s="77"/>
-      <c r="G95" s="77"/>
-      <c r="H95" s="78"/>
+      <c r="A95" s="74"/>
+      <c r="B95" s="75"/>
+      <c r="C95" s="75"/>
+      <c r="D95" s="75"/>
+      <c r="E95" s="75"/>
+      <c r="F95" s="75"/>
+      <c r="G95" s="75"/>
+      <c r="H95" s="76"/>
     </row>
     <row r="96" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A96" s="76"/>
-      <c r="B96" s="77"/>
-      <c r="C96" s="77"/>
-      <c r="D96" s="77"/>
-      <c r="E96" s="77"/>
-      <c r="F96" s="77"/>
-      <c r="G96" s="77"/>
-      <c r="H96" s="78"/>
+      <c r="A96" s="74"/>
+      <c r="B96" s="75"/>
+      <c r="C96" s="75"/>
+      <c r="D96" s="75"/>
+      <c r="E96" s="75"/>
+      <c r="F96" s="75"/>
+      <c r="G96" s="75"/>
+      <c r="H96" s="76"/>
     </row>
     <row r="97" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A97" s="76"/>
-      <c r="B97" s="77"/>
-      <c r="C97" s="77"/>
-      <c r="D97" s="77"/>
-      <c r="E97" s="77"/>
-      <c r="F97" s="77"/>
-      <c r="G97" s="77"/>
-      <c r="H97" s="78"/>
+      <c r="A97" s="74"/>
+      <c r="B97" s="75"/>
+      <c r="C97" s="75"/>
+      <c r="D97" s="75"/>
+      <c r="E97" s="75"/>
+      <c r="F97" s="75"/>
+      <c r="G97" s="75"/>
+      <c r="H97" s="76"/>
     </row>
     <row r="98" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A98" s="76"/>
-      <c r="B98" s="77"/>
-      <c r="C98" s="77"/>
-      <c r="D98" s="77"/>
-      <c r="E98" s="77"/>
-      <c r="F98" s="77"/>
-      <c r="G98" s="77"/>
-      <c r="H98" s="78"/>
+      <c r="A98" s="74"/>
+      <c r="B98" s="75"/>
+      <c r="C98" s="75"/>
+      <c r="D98" s="75"/>
+      <c r="E98" s="75"/>
+      <c r="F98" s="75"/>
+      <c r="G98" s="75"/>
+      <c r="H98" s="76"/>
     </row>
     <row r="99" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A99" s="76"/>
-      <c r="B99" s="77"/>
-      <c r="C99" s="77"/>
-      <c r="D99" s="77"/>
-      <c r="E99" s="77"/>
-      <c r="F99" s="77"/>
-      <c r="G99" s="77"/>
-      <c r="H99" s="78"/>
+      <c r="A99" s="74"/>
+      <c r="B99" s="75"/>
+      <c r="C99" s="75"/>
+      <c r="D99" s="75"/>
+      <c r="E99" s="75"/>
+      <c r="F99" s="75"/>
+      <c r="G99" s="75"/>
+      <c r="H99" s="76"/>
     </row>
     <row r="100" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A100" s="76"/>
-      <c r="B100" s="77"/>
-      <c r="C100" s="77"/>
-      <c r="D100" s="77"/>
-      <c r="E100" s="77"/>
-      <c r="F100" s="77"/>
-      <c r="G100" s="77"/>
-      <c r="H100" s="78"/>
+      <c r="A100" s="74"/>
+      <c r="B100" s="75"/>
+      <c r="C100" s="75"/>
+      <c r="D100" s="75"/>
+      <c r="E100" s="75"/>
+      <c r="F100" s="75"/>
+      <c r="G100" s="75"/>
+      <c r="H100" s="76"/>
     </row>
     <row r="101" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A101" s="76"/>
-      <c r="B101" s="77"/>
-      <c r="C101" s="77"/>
-      <c r="D101" s="77"/>
-      <c r="E101" s="77"/>
-      <c r="F101" s="77"/>
-      <c r="G101" s="77"/>
-      <c r="H101" s="78"/>
+      <c r="A101" s="74"/>
+      <c r="B101" s="75"/>
+      <c r="C101" s="75"/>
+      <c r="D101" s="75"/>
+      <c r="E101" s="75"/>
+      <c r="F101" s="75"/>
+      <c r="G101" s="75"/>
+      <c r="H101" s="76"/>
     </row>
     <row r="102" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A102" s="76"/>
-      <c r="B102" s="77"/>
-      <c r="C102" s="77"/>
-      <c r="D102" s="77"/>
-      <c r="E102" s="77"/>
-      <c r="F102" s="77"/>
-      <c r="G102" s="77"/>
-      <c r="H102" s="78"/>
+      <c r="A102" s="74"/>
+      <c r="B102" s="75"/>
+      <c r="C102" s="75"/>
+      <c r="D102" s="75"/>
+      <c r="E102" s="75"/>
+      <c r="F102" s="75"/>
+      <c r="G102" s="75"/>
+      <c r="H102" s="76"/>
     </row>
     <row r="103" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A103" s="76"/>
-      <c r="B103" s="77"/>
-      <c r="C103" s="77"/>
-      <c r="D103" s="77"/>
-      <c r="E103" s="77"/>
-      <c r="F103" s="77"/>
-      <c r="G103" s="77"/>
-      <c r="H103" s="78"/>
+      <c r="A103" s="74"/>
+      <c r="B103" s="75"/>
+      <c r="C103" s="75"/>
+      <c r="D103" s="75"/>
+      <c r="E103" s="75"/>
+      <c r="F103" s="75"/>
+      <c r="G103" s="75"/>
+      <c r="H103" s="76"/>
     </row>
     <row r="104" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A104" s="76"/>
-      <c r="B104" s="77"/>
-      <c r="C104" s="77"/>
-      <c r="D104" s="77"/>
-      <c r="E104" s="77"/>
-      <c r="F104" s="77"/>
-      <c r="G104" s="77"/>
-      <c r="H104" s="78"/>
+      <c r="A104" s="74"/>
+      <c r="B104" s="75"/>
+      <c r="C104" s="75"/>
+      <c r="D104" s="75"/>
+      <c r="E104" s="75"/>
+      <c r="F104" s="75"/>
+      <c r="G104" s="75"/>
+      <c r="H104" s="76"/>
     </row>
     <row r="105" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A105" s="76"/>
-      <c r="B105" s="77"/>
-      <c r="C105" s="77"/>
-      <c r="D105" s="77"/>
-      <c r="E105" s="77"/>
-      <c r="F105" s="77"/>
-      <c r="G105" s="77"/>
-      <c r="H105" s="78"/>
+      <c r="A105" s="74"/>
+      <c r="B105" s="75"/>
+      <c r="C105" s="75"/>
+      <c r="D105" s="75"/>
+      <c r="E105" s="75"/>
+      <c r="F105" s="75"/>
+      <c r="G105" s="75"/>
+      <c r="H105" s="76"/>
     </row>
     <row r="106" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A106" s="76"/>
-      <c r="B106" s="77"/>
-      <c r="C106" s="77"/>
-      <c r="D106" s="77"/>
-      <c r="E106" s="77"/>
-      <c r="F106" s="77"/>
-      <c r="G106" s="77"/>
-      <c r="H106" s="78"/>
+      <c r="A106" s="74"/>
+      <c r="B106" s="75"/>
+      <c r="C106" s="75"/>
+      <c r="D106" s="75"/>
+      <c r="E106" s="75"/>
+      <c r="F106" s="75"/>
+      <c r="G106" s="75"/>
+      <c r="H106" s="76"/>
     </row>
     <row r="107" spans="1:8" ht="24.6" customHeight="1">
-      <c r="A107" s="79"/>
-      <c r="B107" s="80"/>
-      <c r="C107" s="80"/>
-      <c r="D107" s="80"/>
-      <c r="E107" s="80"/>
-      <c r="F107" s="80"/>
-      <c r="G107" s="80"/>
-      <c r="H107" s="81"/>
+      <c r="A107" s="77"/>
+      <c r="B107" s="78"/>
+      <c r="C107" s="78"/>
+      <c r="D107" s="78"/>
+      <c r="E107" s="78"/>
+      <c r="F107" s="78"/>
+      <c r="G107" s="78"/>
+      <c r="H107" s="79"/>
     </row>
     <row r="108" spans="1:8" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A108" s="82"/>
-      <c r="B108" s="83"/>
-      <c r="C108" s="83"/>
-      <c r="D108" s="83"/>
-      <c r="E108" s="83"/>
-      <c r="F108" s="83"/>
-      <c r="G108" s="83"/>
-      <c r="H108" s="84"/>
+      <c r="A108" s="80"/>
+      <c r="B108" s="81"/>
+      <c r="C108" s="81"/>
+      <c r="D108" s="81"/>
+      <c r="E108" s="81"/>
+      <c r="F108" s="81"/>
+      <c r="G108" s="81"/>
+      <c r="H108" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="H11:H12"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="A11:A12"/>
@@ -3355,6 +3344,11 @@
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="H11:H12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Apps\Recipe Generator App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CA3EC4-41C9-4B6F-8DA9-4B1E078983E4}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A767BAAA-D561-45FA-84E1-76415138B2BE}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1815" yWindow="1815" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample" sheetId="1" r:id="rId1"/>
@@ -108,6 +108,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="15">
     <font>
       <sz val="11"/>
@@ -685,7 +688,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -838,9 +841,31 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -856,26 +881,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1406,9 +1412,9 @@
   <sheetData>
     <row r="1" spans="1:26" ht="24.6" customHeight="1">
       <c r="A1" s="12"/>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
       <c r="E1" s="53"/>
       <c r="F1" s="53"/>
       <c r="G1" s="53"/>
@@ -1419,19 +1425,19 @@
       <c r="A2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="95"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
       <c r="E2" s="45"/>
       <c r="F2" s="45"/>
       <c r="G2" s="45"/>
       <c r="H2" s="14"/>
     </row>
     <row r="3" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A3" s="86"/>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
+      <c r="A3" s="93"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
       <c r="E3" s="45"/>
       <c r="F3" s="46"/>
       <c r="G3" s="46"/>
@@ -1460,10 +1466,10 @@
       <c r="H5" s="14"/>
     </row>
     <row r="6" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A6" s="86"/>
-      <c r="B6" s="87"/>
-      <c r="C6" s="87"/>
-      <c r="D6" s="87"/>
+      <c r="A6" s="93"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
       <c r="E6" s="47"/>
       <c r="F6" s="45"/>
       <c r="G6" s="46"/>
@@ -1474,10 +1480,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="57"/>
-      <c r="C7" s="97" t="s">
+      <c r="C7" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="97"/>
+      <c r="D7" s="91"/>
       <c r="E7" s="57"/>
       <c r="F7" s="58" t="s">
         <v>3</v>
@@ -1488,14 +1494,14 @@
     <row r="8" spans="1:26" ht="33.6" customHeight="1">
       <c r="A8" s="36"/>
       <c r="B8" s="57"/>
-      <c r="C8" s="98"/>
-      <c r="D8" s="98"/>
+      <c r="C8" s="92"/>
+      <c r="D8" s="92"/>
       <c r="E8" s="57"/>
-      <c r="F8" s="96" t="e">
+      <c r="F8" s="88" t="e">
         <f>A8/C8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G8" s="96"/>
+      <c r="G8" s="88"/>
       <c r="H8" s="14"/>
     </row>
     <row r="9" spans="1:26" ht="24.6" customHeight="1">
@@ -1522,28 +1528,28 @@
       <c r="H10" s="14"/>
     </row>
     <row r="11" spans="1:26" ht="24.6" customHeight="1">
-      <c r="A11" s="92" t="s">
+      <c r="A11" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="92" t="s">
+      <c r="B11" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="92" t="s">
+      <c r="C11" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="92" t="s">
+      <c r="D11" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="92" t="s">
+      <c r="E11" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="92" t="s">
+      <c r="F11" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="92" t="s">
+      <c r="G11" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="92" t="s">
+      <c r="H11" s="89" t="s">
         <v>13</v>
       </c>
       <c r="I11" s="3"/>
@@ -1566,14 +1572,14 @@
       <c r="Z11" s="3"/>
     </row>
     <row r="12" spans="1:26" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A12" s="93"/>
-      <c r="B12" s="93"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
+      <c r="A12" s="90"/>
+      <c r="B12" s="90"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="90"/>
+      <c r="E12" s="90"/>
+      <c r="F12" s="90"/>
+      <c r="G12" s="90"/>
+      <c r="H12" s="90"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -1599,7 +1605,7 @@
       <c r="C13" s="34"/>
       <c r="D13" s="34"/>
       <c r="E13" s="34"/>
-      <c r="F13" s="30" t="e">
+      <c r="F13" s="100" t="e">
         <f>E13/C13</f>
         <v>#DIV/0!</v>
       </c>
@@ -1633,7 +1639,7 @@
       <c r="C14" s="34"/>
       <c r="D14" s="34"/>
       <c r="E14" s="34"/>
-      <c r="F14" s="30" t="e">
+      <c r="F14" s="100" t="e">
         <f t="shared" ref="F14:F40" si="0">E14/C14</f>
         <v>#DIV/0!</v>
       </c>
@@ -1667,7 +1673,7 @@
       <c r="C15" s="34"/>
       <c r="D15" s="34"/>
       <c r="E15" s="34"/>
-      <c r="F15" s="30" t="e">
+      <c r="F15" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -1701,7 +1707,7 @@
       <c r="C16" s="34"/>
       <c r="D16" s="34"/>
       <c r="E16" s="34"/>
-      <c r="F16" s="30" t="e">
+      <c r="F16" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -1735,7 +1741,7 @@
       <c r="C17" s="34"/>
       <c r="D17" s="34"/>
       <c r="E17" s="34"/>
-      <c r="F17" s="30" t="e">
+      <c r="F17" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -1769,7 +1775,7 @@
       <c r="C18" s="34"/>
       <c r="D18" s="34"/>
       <c r="E18" s="34"/>
-      <c r="F18" s="30" t="e">
+      <c r="F18" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -1803,7 +1809,7 @@
       <c r="C19" s="34"/>
       <c r="D19" s="34"/>
       <c r="E19" s="34"/>
-      <c r="F19" s="30" t="e">
+      <c r="F19" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -1837,7 +1843,7 @@
       <c r="C20" s="34"/>
       <c r="D20" s="34"/>
       <c r="E20" s="34"/>
-      <c r="F20" s="30" t="e">
+      <c r="F20" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -1871,7 +1877,7 @@
       <c r="C21" s="34"/>
       <c r="D21" s="34"/>
       <c r="E21" s="34"/>
-      <c r="F21" s="30" t="e">
+      <c r="F21" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -1905,7 +1911,7 @@
       <c r="C22" s="34"/>
       <c r="D22" s="34"/>
       <c r="E22" s="34"/>
-      <c r="F22" s="30" t="e">
+      <c r="F22" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -1939,7 +1945,7 @@
       <c r="C23" s="34"/>
       <c r="D23" s="34"/>
       <c r="E23" s="34"/>
-      <c r="F23" s="30" t="e">
+      <c r="F23" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -1973,7 +1979,7 @@
       <c r="C24" s="34"/>
       <c r="D24" s="34"/>
       <c r="E24" s="41"/>
-      <c r="F24" s="30" t="e">
+      <c r="F24" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2007,7 +2013,7 @@
       <c r="C25" s="34"/>
       <c r="D25" s="34"/>
       <c r="E25" s="41"/>
-      <c r="F25" s="30" t="e">
+      <c r="F25" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2041,7 +2047,7 @@
       <c r="C26" s="34"/>
       <c r="D26" s="34"/>
       <c r="E26" s="41"/>
-      <c r="F26" s="30" t="e">
+      <c r="F26" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2075,7 +2081,7 @@
       <c r="C27" s="34"/>
       <c r="D27" s="34"/>
       <c r="E27" s="41"/>
-      <c r="F27" s="30" t="e">
+      <c r="F27" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2109,7 +2115,7 @@
       <c r="C28" s="34"/>
       <c r="D28" s="34"/>
       <c r="E28" s="41"/>
-      <c r="F28" s="30" t="e">
+      <c r="F28" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2143,7 +2149,7 @@
       <c r="C29" s="34"/>
       <c r="D29" s="34"/>
       <c r="E29" s="41"/>
-      <c r="F29" s="30" t="e">
+      <c r="F29" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2177,7 +2183,7 @@
       <c r="C30" s="34"/>
       <c r="D30" s="34"/>
       <c r="E30" s="41"/>
-      <c r="F30" s="30" t="e">
+      <c r="F30" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2211,7 +2217,7 @@
       <c r="C31" s="34"/>
       <c r="D31" s="34"/>
       <c r="E31" s="41"/>
-      <c r="F31" s="30" t="e">
+      <c r="F31" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2245,7 +2251,7 @@
       <c r="C32" s="41"/>
       <c r="D32" s="41"/>
       <c r="E32" s="41"/>
-      <c r="F32" s="30" t="e">
+      <c r="F32" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2279,7 +2285,7 @@
       <c r="C33" s="41"/>
       <c r="D33" s="41"/>
       <c r="E33" s="41"/>
-      <c r="F33" s="30" t="e">
+      <c r="F33" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2313,7 +2319,7 @@
       <c r="C34" s="41"/>
       <c r="D34" s="41"/>
       <c r="E34" s="41"/>
-      <c r="F34" s="30" t="e">
+      <c r="F34" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2347,7 +2353,7 @@
       <c r="C35" s="41"/>
       <c r="D35" s="41"/>
       <c r="E35" s="41"/>
-      <c r="F35" s="30" t="e">
+      <c r="F35" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2381,7 +2387,7 @@
       <c r="C36" s="41"/>
       <c r="D36" s="41"/>
       <c r="E36" s="41"/>
-      <c r="F36" s="30" t="e">
+      <c r="F36" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2415,7 +2421,7 @@
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
-      <c r="F37" s="30" t="e">
+      <c r="F37" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2449,7 +2455,7 @@
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
-      <c r="F38" s="30" t="e">
+      <c r="F38" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2483,7 +2489,7 @@
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
-      <c r="F39" s="30" t="e">
+      <c r="F39" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2517,7 +2523,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
-      <c r="F40" s="30" t="e">
+      <c r="F40" s="100" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2786,10 +2792,10 @@
       <c r="H54" s="24"/>
     </row>
     <row r="55" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A55" s="86"/>
-      <c r="B55" s="87"/>
-      <c r="C55" s="87"/>
-      <c r="D55" s="87"/>
+      <c r="A55" s="93"/>
+      <c r="B55" s="95"/>
+      <c r="C55" s="95"/>
+      <c r="D55" s="95"/>
       <c r="E55" s="45"/>
       <c r="F55" s="46"/>
       <c r="G55" s="46"/>
@@ -2818,10 +2824,10 @@
       <c r="H57" s="14"/>
     </row>
     <row r="58" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A58" s="86"/>
-      <c r="B58" s="87"/>
-      <c r="C58" s="87"/>
-      <c r="D58" s="87"/>
+      <c r="A58" s="93"/>
+      <c r="B58" s="95"/>
+      <c r="C58" s="95"/>
+      <c r="D58" s="95"/>
       <c r="E58" s="47"/>
       <c r="F58" s="45"/>
       <c r="G58" s="46"/>
@@ -2830,24 +2836,24 @@
     <row r="59" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
       <c r="A59" s="48"/>
       <c r="B59" s="49"/>
-      <c r="C59" s="91"/>
-      <c r="D59" s="91"/>
+      <c r="C59" s="99"/>
+      <c r="D59" s="99"/>
       <c r="E59" s="49"/>
       <c r="F59" s="50"/>
       <c r="G59" s="50"/>
       <c r="H59" s="51"/>
     </row>
     <row r="60" spans="1:10" ht="24.6" customHeight="1" thickBot="1">
-      <c r="A60" s="88" t="s">
+      <c r="A60" s="96" t="s">
         <v>23</v>
       </c>
-      <c r="B60" s="89"/>
-      <c r="C60" s="89"/>
-      <c r="D60" s="89"/>
-      <c r="E60" s="89"/>
-      <c r="F60" s="89"/>
-      <c r="G60" s="89"/>
-      <c r="H60" s="90"/>
+      <c r="B60" s="97"/>
+      <c r="C60" s="97"/>
+      <c r="D60" s="97"/>
+      <c r="E60" s="97"/>
+      <c r="F60" s="97"/>
+      <c r="G60" s="97"/>
+      <c r="H60" s="98"/>
     </row>
     <row r="61" spans="1:10" ht="24.6" customHeight="1">
       <c r="A61" s="74"/>
@@ -3331,6 +3337,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="H11:H12"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="A11:A12"/>
@@ -3344,11 +3355,6 @@
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="H11:H12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>
